--- a/data/data_clustered.xlsx
+++ b/data/data_clustered.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>Ratio MeOH/Fa</t>
+          <t>Ratio Stab/Fa</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
@@ -793,14 +793,10 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
         <v>5</v>
       </c>
@@ -953,12 +949,12 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM3" t="n">
@@ -1103,12 +1099,12 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM4" t="n">
@@ -1253,12 +1249,12 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM5" t="n">
@@ -1403,12 +1399,12 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM6" t="n">
@@ -1565,14 +1561,10 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="n">
         <v>2.5</v>
       </c>
@@ -1725,14 +1717,10 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="n">
         <v>2.5</v>
       </c>
@@ -1885,12 +1873,12 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM9" t="n">
@@ -2047,12 +2035,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM10" t="n">
@@ -2209,12 +2197,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM11" t="n">
@@ -2371,12 +2359,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM12" t="n">
@@ -2533,12 +2521,12 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM13" t="n">
@@ -2695,12 +2683,12 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM14" t="n">
@@ -2857,12 +2845,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM15" t="n">
@@ -3019,12 +3007,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM16" t="n">
@@ -3181,12 +3169,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM17" t="n">
@@ -3343,12 +3331,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM18" t="n">
@@ -3505,12 +3493,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM19" t="n">
@@ -3665,12 +3653,12 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM20" t="n">
@@ -3825,12 +3813,12 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM21" t="n">
@@ -3985,12 +3973,12 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM22" t="n">
@@ -4145,12 +4133,12 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM23" t="n">
@@ -4305,12 +4293,12 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM24" t="n">
@@ -4465,12 +4453,12 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM25" t="n">
@@ -4625,12 +4613,12 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM26" t="n">
@@ -4785,12 +4773,12 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM27" t="n">
@@ -4947,12 +4935,12 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM28" t="n">
@@ -5109,12 +5097,12 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM29" t="n">
@@ -5271,12 +5259,12 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM30" t="n">
@@ -5433,14 +5421,10 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr"/>
       <c r="AM31" t="n">
         <v>5</v>
       </c>
@@ -5585,14 +5569,10 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr"/>
       <c r="AM32" t="n">
         <v>5</v>
       </c>
@@ -5745,14 +5725,10 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr"/>
       <c r="AM33" t="n">
         <v>5</v>
       </c>
@@ -5905,14 +5881,10 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="n">
         <v>5</v>
       </c>
@@ -6065,12 +6037,12 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM35" t="n">
@@ -6225,12 +6197,12 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM36" t="n">
@@ -6385,12 +6357,12 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM37" t="n">
@@ -6545,12 +6517,12 @@
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM38" t="n">
@@ -6708,11 +6680,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL39" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL39" t="inlineStr"/>
       <c r="AM39" t="n">
         <v>0.5</v>
       </c>
@@ -6857,12 +6825,12 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM40" t="n">
@@ -7019,12 +6987,12 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM41" t="n">
@@ -7179,14 +7147,10 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="n">
         <v>10</v>
       </c>
@@ -7329,14 +7293,10 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr"/>
       <c r="AM43" t="n">
         <v>3</v>
       </c>
@@ -7489,14 +7449,10 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL44" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL44" t="inlineStr"/>
       <c r="AM44" t="n">
         <v>3</v>
       </c>
@@ -7649,14 +7605,10 @@
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL45" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr"/>
       <c r="AM45" t="n">
         <v>3</v>
       </c>
@@ -7809,14 +7761,10 @@
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL46" t="inlineStr"/>
       <c r="AM46" t="n">
         <v>3</v>
       </c>
@@ -7969,12 +7917,12 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM47" t="n">
@@ -8125,14 +8073,10 @@
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr"/>
       <c r="AM48" t="n">
         <v>10</v>
       </c>
@@ -8275,12 +8219,12 @@
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM49" t="n">
@@ -8437,14 +8381,10 @@
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL50" t="inlineStr"/>
       <c r="AM50" t="n">
         <v>5</v>
       </c>
@@ -8597,14 +8537,10 @@
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL51" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr"/>
       <c r="AM51" t="n">
         <v>5</v>
       </c>
@@ -8757,14 +8693,10 @@
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL52" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr"/>
       <c r="AM52" t="n">
         <v>5</v>
       </c>
@@ -8917,12 +8849,12 @@
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>Ethanol</t>
+          <t>EtOH</t>
         </is>
       </c>
       <c r="AM53" t="n">
@@ -9073,12 +9005,12 @@
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>Ethanol</t>
+          <t>EtOH</t>
         </is>
       </c>
       <c r="AM54" t="n">
@@ -9229,12 +9161,12 @@
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>Ethanol</t>
+          <t>EtOH</t>
         </is>
       </c>
       <c r="AM55" t="n">
@@ -9385,12 +9317,12 @@
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM56" t="n">
@@ -9547,12 +9479,12 @@
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM57" t="n">
@@ -9709,12 +9641,12 @@
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM58" t="n">
@@ -9871,12 +9803,12 @@
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM59" t="n">
@@ -10031,12 +9963,12 @@
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM60" t="n">
@@ -10191,12 +10123,12 @@
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM61" t="n">
@@ -10351,12 +10283,12 @@
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM62" t="n">
@@ -10511,12 +10443,12 @@
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM63" t="n">
@@ -10673,12 +10605,12 @@
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM64" t="n">
@@ -10835,12 +10767,12 @@
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM65" t="n">
@@ -10997,12 +10929,12 @@
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL66" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM66" t="n">
@@ -11159,12 +11091,12 @@
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL67" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM67" t="n">
@@ -11321,12 +11253,12 @@
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM68" t="n">
@@ -11483,12 +11415,12 @@
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM69" t="n">
@@ -11645,14 +11577,10 @@
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL70" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL70" t="inlineStr"/>
       <c r="AM70" t="n">
         <v>5</v>
       </c>
@@ -11805,14 +11733,10 @@
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL71" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL71" t="inlineStr"/>
       <c r="AM71" t="n">
         <v>5</v>
       </c>
@@ -11965,12 +11889,12 @@
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM72" t="n">
@@ -12117,12 +12041,12 @@
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM73" t="n">
@@ -12269,12 +12193,12 @@
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM74" t="n">
@@ -12421,14 +12345,10 @@
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL75" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL75" t="inlineStr"/>
       <c r="AM75" t="n">
         <v>0.5</v>
       </c>
@@ -12581,14 +12501,10 @@
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL76" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL76" t="inlineStr"/>
       <c r="AM76" t="n">
         <v>2</v>
       </c>
@@ -12741,12 +12657,12 @@
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM77" t="n">
@@ -12903,14 +12819,10 @@
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL78" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL78" t="inlineStr"/>
       <c r="AM78" t="n">
         <v>5</v>
       </c>
@@ -13063,14 +12975,10 @@
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL79" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL79" t="inlineStr"/>
       <c r="AM79" t="n">
         <v>5</v>
       </c>
@@ -13223,12 +13131,12 @@
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL80" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM80" t="n">
@@ -13375,12 +13283,12 @@
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL81" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM81" t="n">
@@ -13527,12 +13435,12 @@
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM82" t="n">
@@ -13689,12 +13597,12 @@
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL83" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM83" t="n">
@@ -13851,12 +13759,12 @@
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL84" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM84" t="n">
@@ -14013,12 +13921,12 @@
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL85" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM85" t="n">
@@ -14175,12 +14083,12 @@
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL86" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM86" t="n">
@@ -14337,12 +14245,12 @@
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM87" t="n">
@@ -14499,12 +14407,12 @@
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL88" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM88" t="n">
@@ -14661,12 +14569,12 @@
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM89" t="n">
@@ -14823,12 +14731,12 @@
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL90" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM90" t="n">
@@ -14985,12 +14893,12 @@
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM91" t="n">
@@ -15145,12 +15053,12 @@
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL92" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM92" t="n">
@@ -15305,12 +15213,12 @@
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL93" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM93" t="n">
@@ -15465,12 +15373,12 @@
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL94" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM94" t="n">
@@ -15625,12 +15533,12 @@
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL95" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM95" t="n">
@@ -15785,12 +15693,12 @@
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM96" t="n">
@@ -15945,12 +15853,12 @@
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM97" t="n">
@@ -16105,12 +16013,12 @@
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL98" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM98" t="n">
@@ -16265,12 +16173,12 @@
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL99" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM99" t="n">
@@ -16425,12 +16333,12 @@
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL100" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM100" t="n">
@@ -16585,12 +16493,12 @@
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL101" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM101" t="n">
@@ -16745,14 +16653,10 @@
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL102" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL102" t="inlineStr"/>
       <c r="AM102" t="n">
         <v>10</v>
       </c>
@@ -16895,14 +16799,10 @@
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL103" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL103" t="inlineStr"/>
       <c r="AM103" t="n">
         <v>10</v>
       </c>
@@ -17045,14 +16945,10 @@
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL104" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL104" t="inlineStr"/>
       <c r="AM104" t="n">
         <v>10</v>
       </c>
@@ -17195,14 +17091,10 @@
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL105" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL105" t="inlineStr"/>
       <c r="AM105" t="n">
         <v>10</v>
       </c>
@@ -17345,14 +17237,10 @@
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL106" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL106" t="inlineStr"/>
       <c r="AM106" t="n">
         <v>10</v>
       </c>
@@ -17495,14 +17383,10 @@
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL107" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL107" t="inlineStr"/>
       <c r="AM107" t="n">
         <v>10</v>
       </c>
@@ -17645,14 +17529,10 @@
       </c>
       <c r="AK108" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL108" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL108" t="inlineStr"/>
       <c r="AM108" t="n">
         <v>10</v>
       </c>
@@ -17795,14 +17675,10 @@
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL109" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL109" t="inlineStr"/>
       <c r="AM109" t="n">
         <v>10</v>
       </c>
@@ -17945,14 +17821,10 @@
       </c>
       <c r="AK110" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL110" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL110" t="inlineStr"/>
       <c r="AM110" t="n">
         <v>10</v>
       </c>
@@ -18095,14 +17967,10 @@
       </c>
       <c r="AK111" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL111" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL111" t="inlineStr"/>
       <c r="AM111" t="n">
         <v>10</v>
       </c>
@@ -18245,14 +18113,10 @@
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL112" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL112" t="inlineStr"/>
       <c r="AM112" t="n">
         <v>10</v>
       </c>
@@ -18395,14 +18259,10 @@
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL113" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL113" t="inlineStr"/>
       <c r="AM113" t="n">
         <v>5</v>
       </c>
@@ -18560,11 +18420,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL114" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL114" t="inlineStr"/>
       <c r="AM114" t="n">
         <v>0.5</v>
       </c>
@@ -18711,14 +18567,10 @@
       </c>
       <c r="AK115" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL115" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL115" t="inlineStr"/>
       <c r="AM115" t="n">
         <v>5</v>
       </c>
@@ -18876,11 +18728,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL116" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL116" t="inlineStr"/>
       <c r="AM116" t="n">
         <v>0.5</v>
       </c>
@@ -19030,11 +18878,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL117" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL117" t="inlineStr"/>
       <c r="AM117" t="n">
         <v>0.5</v>
       </c>
@@ -19181,14 +19025,10 @@
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL118" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL118" t="inlineStr"/>
       <c r="AM118" t="n">
         <v>5</v>
       </c>
@@ -19346,11 +19186,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL119" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL119" t="inlineStr"/>
       <c r="AM119" t="n">
         <v>0.5</v>
       </c>
@@ -19500,11 +19336,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL120" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL120" t="inlineStr"/>
       <c r="AM120" t="n">
         <v>2</v>
       </c>
@@ -19654,11 +19486,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL121" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL121" t="inlineStr"/>
       <c r="AM121" t="n">
         <v>0.5</v>
       </c>
@@ -19808,11 +19636,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL122" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL122" t="inlineStr"/>
       <c r="AM122" t="n">
         <v>0.5</v>
       </c>
@@ -19960,11 +19784,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL123" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL123" t="inlineStr"/>
       <c r="AM123" t="n">
         <v>0.5</v>
       </c>
@@ -20112,11 +19932,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL124" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL124" t="inlineStr"/>
       <c r="AM124" t="n">
         <v>0.5</v>
       </c>
@@ -20264,11 +20080,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL125" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL125" t="inlineStr"/>
       <c r="AM125" t="n">
         <v>0.5</v>
       </c>
@@ -20416,11 +20228,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL126" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL126" t="inlineStr"/>
       <c r="AM126" t="n">
         <v>0.5</v>
       </c>
@@ -20565,14 +20373,10 @@
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL127" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL127" t="inlineStr"/>
       <c r="AM127" t="n">
         <v>5</v>
       </c>
@@ -20725,14 +20529,10 @@
       </c>
       <c r="AK128" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL128" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL128" t="inlineStr"/>
       <c r="AM128" t="n">
         <v>5</v>
       </c>
@@ -20885,14 +20685,10 @@
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL129" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL129" t="inlineStr"/>
       <c r="AM129" t="n">
         <v>5</v>
       </c>
@@ -21045,14 +20841,10 @@
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL130" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL130" t="inlineStr"/>
       <c r="AM130" t="n">
         <v>5</v>
       </c>
@@ -21208,11 +21000,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL131" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL131" t="inlineStr"/>
       <c r="AM131" t="n">
         <v>0.5</v>
       </c>
@@ -21359,12 +21147,12 @@
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL132" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM132" t="n">
@@ -21511,12 +21299,12 @@
       </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL133" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM133" t="n">
@@ -21663,14 +21451,10 @@
       </c>
       <c r="AK134" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL134" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL134" t="inlineStr"/>
       <c r="AM134" t="n">
         <v>10</v>
       </c>
@@ -21813,14 +21597,10 @@
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL135" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL135" t="inlineStr"/>
       <c r="AM135" t="n">
         <v>2.5</v>
       </c>
@@ -21973,14 +21753,10 @@
       </c>
       <c r="AK136" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL136" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL136" t="inlineStr"/>
       <c r="AM136" t="n">
         <v>3</v>
       </c>
@@ -22133,12 +21909,12 @@
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL137" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM137" t="n">
@@ -22285,14 +22061,10 @@
       </c>
       <c r="AK138" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL138" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL138" t="inlineStr"/>
       <c r="AM138" t="n">
         <v>5</v>
       </c>
@@ -22445,14 +22217,10 @@
       </c>
       <c r="AK139" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL139" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL139" t="inlineStr"/>
       <c r="AM139" t="n">
         <v>2.5</v>
       </c>
@@ -22605,14 +22373,10 @@
       </c>
       <c r="AK140" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL140" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL140" t="inlineStr"/>
       <c r="AM140" t="n">
         <v>5</v>
       </c>
@@ -22765,14 +22529,10 @@
       </c>
       <c r="AK141" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL141" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL141" t="inlineStr"/>
       <c r="AM141" t="n">
         <v>5</v>
       </c>
@@ -22925,12 +22685,12 @@
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL142" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM142" t="n">
@@ -23077,14 +22837,10 @@
       </c>
       <c r="AK143" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL143" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL143" t="inlineStr"/>
       <c r="AM143" t="n">
         <v>5</v>
       </c>
@@ -23237,14 +22993,10 @@
       </c>
       <c r="AK144" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL144" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL144" t="inlineStr"/>
       <c r="AM144" t="n">
         <v>0.5</v>
       </c>
@@ -23397,12 +23149,12 @@
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL145" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM145" t="n">
@@ -23559,12 +23311,12 @@
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL146" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM146" t="n">
@@ -23721,14 +23473,10 @@
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL147" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL147" t="inlineStr"/>
       <c r="AM147" t="n">
         <v>10</v>
       </c>
@@ -23871,14 +23619,10 @@
       </c>
       <c r="AK148" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL148" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL148" t="inlineStr"/>
       <c r="AM148" t="n">
         <v>10</v>
       </c>
@@ -24021,14 +23765,10 @@
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL149" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL149" t="inlineStr"/>
       <c r="AM149" t="n">
         <v>10</v>
       </c>
@@ -24171,14 +23911,10 @@
       </c>
       <c r="AK150" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL150" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL150" t="inlineStr"/>
       <c r="AM150" t="n">
         <v>10</v>
       </c>
@@ -24321,14 +24057,10 @@
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL151" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL151" t="inlineStr"/>
       <c r="AM151" t="n">
         <v>10</v>
       </c>
@@ -24471,14 +24203,10 @@
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL152" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL152" t="inlineStr"/>
       <c r="AM152" t="n">
         <v>10</v>
       </c>
@@ -24621,14 +24349,10 @@
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL153" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL153" t="inlineStr"/>
       <c r="AM153" t="n">
         <v>10</v>
       </c>
@@ -24771,14 +24495,10 @@
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL154" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL154" t="inlineStr"/>
       <c r="AM154" t="n">
         <v>10</v>
       </c>
@@ -24921,14 +24641,10 @@
       </c>
       <c r="AK155" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL155" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL155" t="inlineStr"/>
       <c r="AM155" t="n">
         <v>10</v>
       </c>
@@ -25071,12 +24787,12 @@
       </c>
       <c r="AK156" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL156" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM156" t="n">
@@ -25223,12 +24939,12 @@
       </c>
       <c r="AK157" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL157" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM157" t="n">
@@ -25375,12 +25091,12 @@
       </c>
       <c r="AK158" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL158" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM158" t="n">
@@ -25527,12 +25243,12 @@
       </c>
       <c r="AK159" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL159" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM159" t="n">
@@ -25679,14 +25395,10 @@
       </c>
       <c r="AK160" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL160" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL160" t="inlineStr"/>
       <c r="AM160" t="n">
         <v>5</v>
       </c>
@@ -25839,12 +25551,12 @@
       </c>
       <c r="AK161" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL161" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM161" t="n">
@@ -26001,14 +25713,10 @@
       </c>
       <c r="AK162" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL162" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL162" t="inlineStr"/>
       <c r="AM162" t="n">
         <v>2.5</v>
       </c>
@@ -26161,12 +25869,12 @@
       </c>
       <c r="AK163" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL163" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM163" t="n">
@@ -26323,12 +26031,12 @@
       </c>
       <c r="AK164" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL164" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM164" t="n">
@@ -26485,14 +26193,10 @@
       </c>
       <c r="AK165" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL165" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL165" t="inlineStr"/>
       <c r="AM165" t="n">
         <v>5</v>
       </c>
@@ -26645,12 +26349,12 @@
       </c>
       <c r="AK166" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL166" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM166" t="n">
@@ -26807,12 +26511,12 @@
       </c>
       <c r="AK167" t="inlineStr">
         <is>
-          <t>Trioxane</t>
+          <t>TRX</t>
         </is>
       </c>
       <c r="AL167" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM167" t="n">
@@ -26969,14 +26673,10 @@
       </c>
       <c r="AK168" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL168" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL168" t="inlineStr"/>
       <c r="AM168" t="n">
         <v>1</v>
       </c>
@@ -27121,14 +26821,10 @@
       </c>
       <c r="AK169" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL169" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL169" t="inlineStr"/>
       <c r="AM169" t="n">
         <v>1</v>
       </c>
@@ -27273,14 +26969,10 @@
       </c>
       <c r="AK170" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL170" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL170" t="inlineStr"/>
       <c r="AM170" t="n">
         <v>1</v>
       </c>
@@ -27425,14 +27117,10 @@
       </c>
       <c r="AK171" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL171" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL171" t="inlineStr"/>
       <c r="AM171" t="n">
         <v>1</v>
       </c>
@@ -27577,14 +27265,10 @@
       </c>
       <c r="AK172" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL172" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL172" t="inlineStr"/>
       <c r="AM172" t="n">
         <v>1</v>
       </c>
@@ -27729,14 +27413,10 @@
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL173" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL173" t="inlineStr"/>
       <c r="AM173" t="n">
         <v>0.2</v>
       </c>
@@ -27889,14 +27569,10 @@
       </c>
       <c r="AK174" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL174" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL174" t="inlineStr"/>
       <c r="AM174" t="n">
         <v>2.5</v>
       </c>
@@ -28049,14 +27725,10 @@
       </c>
       <c r="AK175" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL175" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL175" t="inlineStr"/>
       <c r="AM175" t="n">
         <v>0.4</v>
       </c>
@@ -28209,14 +27881,10 @@
       </c>
       <c r="AK176" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL176" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL176" t="inlineStr"/>
       <c r="AM176" t="n">
         <v>0.4</v>
       </c>
@@ -28371,14 +28039,10 @@
       </c>
       <c r="AK177" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL177" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL177" t="inlineStr"/>
       <c r="AM177" t="n">
         <v>0.4</v>
       </c>
@@ -28533,14 +28197,10 @@
       </c>
       <c r="AK178" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL178" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL178" t="inlineStr"/>
       <c r="AM178" t="n">
         <v>2.5</v>
       </c>
@@ -28695,14 +28355,10 @@
       </c>
       <c r="AK179" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL179" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL179" t="inlineStr"/>
       <c r="AM179" t="n">
         <v>0.4</v>
       </c>
@@ -28857,14 +28513,10 @@
       </c>
       <c r="AK180" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL180" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL180" t="inlineStr"/>
       <c r="AM180" t="n">
         <v>2.5</v>
       </c>
@@ -29019,14 +28671,10 @@
       </c>
       <c r="AK181" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL181" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL181" t="inlineStr"/>
       <c r="AM181" t="n">
         <v>2.5</v>
       </c>
@@ -29181,14 +28829,10 @@
       </c>
       <c r="AK182" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL182" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL182" t="inlineStr"/>
       <c r="AM182" t="n">
         <v>5</v>
       </c>
@@ -29341,14 +28985,10 @@
       </c>
       <c r="AK183" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL183" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL183" t="inlineStr"/>
       <c r="AM183" t="n">
         <v>5</v>
       </c>
@@ -29501,14 +29141,10 @@
       </c>
       <c r="AK184" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL184" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL184" t="inlineStr"/>
       <c r="AM184" t="n">
         <v>1</v>
       </c>
@@ -29653,14 +29289,10 @@
       </c>
       <c r="AK185" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL185" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL185" t="inlineStr"/>
       <c r="AM185" t="n">
         <v>3</v>
       </c>
@@ -29811,14 +29443,10 @@
       </c>
       <c r="AK186" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL186" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL186" t="inlineStr"/>
       <c r="AM186" t="n">
         <v>3</v>
       </c>
@@ -29969,20 +29597,14 @@
       </c>
       <c r="AK187" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL187" t="inlineStr">
-        <is>
-          <t>Methanol</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL187" t="inlineStr"/>
       <c r="AM187" t="n">
         <v>2.5</v>
       </c>
-      <c r="AN187" t="n">
-        <v>1</v>
-      </c>
+      <c r="AN187" t="inlineStr"/>
       <c r="AO187" t="inlineStr">
         <is>
           <t>97:3</t>
@@ -30001,13 +29623,13 @@
         <v>3</v>
       </c>
       <c r="AT187" t="n">
-        <v>0.3064103049153603</v>
+        <v>0.1018814263843573</v>
       </c>
       <c r="AU187" t="n">
-        <v>0.7660257622884007</v>
+        <v>0.2547035659608932</v>
       </c>
       <c r="AV187" t="n">
-        <v>3.508839222119954</v>
+        <v>1.166689041354884</v>
       </c>
       <c r="AW187" t="n">
         <v>2</v>
@@ -30131,14 +29753,10 @@
       </c>
       <c r="AK188" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL188" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL188" t="inlineStr"/>
       <c r="AM188" t="n">
         <v>3</v>
       </c>
@@ -30291,14 +29909,10 @@
       </c>
       <c r="AK189" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL189" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL189" t="inlineStr"/>
       <c r="AM189" t="n">
         <v>5</v>
       </c>
@@ -30451,14 +30065,10 @@
       </c>
       <c r="AK190" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL190" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL190" t="inlineStr"/>
       <c r="AM190" t="n">
         <v>2.5</v>
       </c>
@@ -30609,14 +30219,10 @@
       </c>
       <c r="AK191" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL191" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL191" t="inlineStr"/>
       <c r="AM191" t="n">
         <v>2.5</v>
       </c>
@@ -30767,14 +30373,10 @@
       </c>
       <c r="AK192" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL192" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL192" t="inlineStr"/>
       <c r="AM192" t="n">
         <v>1.825</v>
       </c>
@@ -30925,14 +30527,10 @@
       </c>
       <c r="AK193" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL193" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL193" t="inlineStr"/>
       <c r="AM193" t="n">
         <v>2.235294117647059</v>
       </c>
@@ -31083,14 +30681,10 @@
       </c>
       <c r="AK194" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL194" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL194" t="inlineStr"/>
       <c r="AM194" t="n">
         <v>2.235294117647059</v>
       </c>
@@ -31241,14 +30835,10 @@
       </c>
       <c r="AK195" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL195" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL195" t="inlineStr"/>
       <c r="AM195" t="n">
         <v>1.813333333333333</v>
       </c>
@@ -31399,14 +30989,10 @@
       </c>
       <c r="AK196" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL196" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL196" t="inlineStr"/>
       <c r="AM196" t="n">
         <v>2.235294117647059</v>
       </c>
@@ -31557,14 +31143,10 @@
       </c>
       <c r="AK197" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL197" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL197" t="inlineStr"/>
       <c r="AM197" t="n">
         <v>2.235294117647059</v>
       </c>
@@ -31715,14 +31297,10 @@
       </c>
       <c r="AK198" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL198" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL198" t="inlineStr"/>
       <c r="AM198" t="n">
         <v>2.235294117647059</v>
       </c>
@@ -31873,14 +31451,10 @@
       </c>
       <c r="AK199" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL199" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL199" t="inlineStr"/>
       <c r="AM199" t="n">
         <v>2.235294117647059</v>
       </c>
@@ -32031,14 +31605,10 @@
       </c>
       <c r="AK200" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL200" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL200" t="inlineStr"/>
       <c r="AM200" t="n">
         <v>2.102857142857143</v>
       </c>
@@ -32189,14 +31759,10 @@
       </c>
       <c r="AK201" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL201" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL201" t="inlineStr"/>
       <c r="AM201" t="n">
         <v>2.102857142857143</v>
       </c>
@@ -32347,14 +31913,10 @@
       </c>
       <c r="AK202" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL202" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL202" t="inlineStr"/>
       <c r="AM202" t="n">
         <v>2.102857142857143</v>
       </c>
@@ -32505,14 +32067,10 @@
       </c>
       <c r="AK203" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL203" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL203" t="inlineStr"/>
       <c r="AM203" t="n">
         <v>2.102857142857143</v>
       </c>
@@ -32663,14 +32221,10 @@
       </c>
       <c r="AK204" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL204" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL204" t="inlineStr"/>
       <c r="AM204" t="n">
         <v>2.102857142857143</v>
       </c>
@@ -32821,14 +32375,10 @@
       </c>
       <c r="AK205" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL205" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL205" t="inlineStr"/>
       <c r="AM205" t="n">
         <v>2.102857142857143</v>
       </c>
@@ -32979,14 +32529,10 @@
       </c>
       <c r="AK206" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL206" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL206" t="inlineStr"/>
       <c r="AM206" t="n">
         <v>2.102857142857143</v>
       </c>
@@ -33137,14 +32683,10 @@
       </c>
       <c r="AK207" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL207" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL207" t="inlineStr"/>
       <c r="AM207" t="n">
         <v>2.102857142857143</v>
       </c>
@@ -33295,14 +32837,10 @@
       </c>
       <c r="AK208" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL208" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL208" t="inlineStr"/>
       <c r="AM208" t="n">
         <v>2.102857142857143</v>
       </c>
@@ -33453,14 +32991,10 @@
       </c>
       <c r="AK209" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL209" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL209" t="inlineStr"/>
       <c r="AM209" t="n">
         <v>2.102857142857143</v>
       </c>
@@ -33614,11 +33148,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL210" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL210" t="inlineStr"/>
       <c r="AM210" t="n">
         <v>2</v>
       </c>
@@ -33768,11 +33298,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL211" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL211" t="inlineStr"/>
       <c r="AM211" t="n">
         <v>2</v>
       </c>
@@ -33922,11 +33448,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL212" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL212" t="inlineStr"/>
       <c r="AM212" t="n">
         <v>2</v>
       </c>
@@ -34076,11 +33598,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL213" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL213" t="inlineStr"/>
       <c r="AM213" t="n">
         <v>2</v>
       </c>
@@ -34229,12 +33747,12 @@
       </c>
       <c r="AK214" t="inlineStr">
         <is>
-          <t>Formalin</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="AL214" t="inlineStr">
         <is>
-          <t>Commercial formalin + methanol</t>
+          <t>MeOH</t>
         </is>
       </c>
       <c r="AM214" t="n">
@@ -34387,14 +33905,10 @@
       </c>
       <c r="AK215" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL215" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL215" t="inlineStr"/>
       <c r="AM215" t="n">
         <v>2.5</v>
       </c>
@@ -34547,14 +34061,10 @@
       </c>
       <c r="AK216" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL216" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL216" t="inlineStr"/>
       <c r="AM216" t="n">
         <v>2.5</v>
       </c>
@@ -34707,14 +34217,10 @@
       </c>
       <c r="AK217" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL217" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL217" t="inlineStr"/>
       <c r="AM217" t="n">
         <v>2.5</v>
       </c>
@@ -34867,14 +34373,10 @@
       </c>
       <c r="AK218" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL218" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL218" t="inlineStr"/>
       <c r="AM218" t="n">
         <v>2.5</v>
       </c>
@@ -35027,14 +34529,10 @@
       </c>
       <c r="AK219" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL219" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL219" t="inlineStr"/>
       <c r="AM219" t="n">
         <v>2.5</v>
       </c>
@@ -35187,14 +34685,10 @@
       </c>
       <c r="AK220" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL220" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL220" t="inlineStr"/>
       <c r="AM220" t="n">
         <v>2.5</v>
       </c>
@@ -35347,14 +34841,10 @@
       </c>
       <c r="AK221" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL221" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL221" t="inlineStr"/>
       <c r="AM221" t="n">
         <v>2.5</v>
       </c>
@@ -35507,14 +34997,10 @@
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL222" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL222" t="inlineStr"/>
       <c r="AM222" t="n">
         <v>2.5</v>
       </c>
@@ -35667,14 +35153,10 @@
       </c>
       <c r="AK223" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL223" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL223" t="inlineStr"/>
       <c r="AM223" t="n">
         <v>2.5</v>
       </c>
@@ -35827,14 +35309,10 @@
       </c>
       <c r="AK224" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL224" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL224" t="inlineStr"/>
       <c r="AM224" t="n">
         <v>2.5</v>
       </c>
@@ -35987,14 +35465,10 @@
       </c>
       <c r="AK225" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL225" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL225" t="inlineStr"/>
       <c r="AM225" t="n">
         <v>2.5</v>
       </c>
@@ -36147,14 +35621,10 @@
       </c>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL226" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL226" t="inlineStr"/>
       <c r="AM226" t="n">
         <v>2.5</v>
       </c>
@@ -36307,14 +35777,10 @@
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL227" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL227" t="inlineStr"/>
       <c r="AM227" t="n">
         <v>2.5</v>
       </c>
@@ -36467,14 +35933,10 @@
       </c>
       <c r="AK228" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL228" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL228" t="inlineStr"/>
       <c r="AM228" t="n">
         <v>2.5</v>
       </c>
@@ -36627,27 +36089,21 @@
       </c>
       <c r="AK229" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL229" t="inlineStr">
-        <is>
-          <t>Methanol</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL229" t="inlineStr"/>
       <c r="AM229" t="n">
         <v>2.5</v>
       </c>
-      <c r="AN229" t="n">
-        <v>1</v>
-      </c>
+      <c r="AN229" t="inlineStr"/>
       <c r="AO229" t="inlineStr">
         <is>
           <t>97:3</t>
         </is>
       </c>
       <c r="AP229" t="n">
-        <v>1.33</v>
+        <v>0.4433333333333334</v>
       </c>
       <c r="AQ229" t="n">
         <v>633</v>
@@ -36659,13 +36115,13 @@
         <v>3</v>
       </c>
       <c r="AT229" t="n">
-        <v>0.3064103049153603</v>
+        <v>0.1018814263843573</v>
       </c>
       <c r="AU229" t="n">
-        <v>0.7660257622884007</v>
+        <v>0.2547035659608932</v>
       </c>
       <c r="AV229" t="n">
-        <v>3.755916235591505</v>
+        <v>1.248842148334175</v>
       </c>
       <c r="AW229" t="n">
         <v>2</v>
@@ -36789,27 +36245,21 @@
       </c>
       <c r="AK230" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL230" t="inlineStr">
-        <is>
-          <t>Methanol</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL230" t="inlineStr"/>
       <c r="AM230" t="n">
         <v>2.5</v>
       </c>
-      <c r="AN230" t="n">
-        <v>1</v>
-      </c>
+      <c r="AN230" t="inlineStr"/>
       <c r="AO230" t="inlineStr">
         <is>
           <t>97:3</t>
         </is>
       </c>
       <c r="AP230" t="n">
-        <v>1.33</v>
+        <v>0.4433333333333334</v>
       </c>
       <c r="AQ230" t="n">
         <v>633</v>
@@ -36821,13 +36271,13 @@
         <v>3</v>
       </c>
       <c r="AT230" t="n">
-        <v>0.3064103049153603</v>
+        <v>0.1018814263843573</v>
       </c>
       <c r="AU230" t="n">
-        <v>0.7660257622884007</v>
+        <v>0.2547035659608932</v>
       </c>
       <c r="AV230" t="n">
-        <v>3.777668609547749</v>
+        <v>1.256074812674627</v>
       </c>
       <c r="AW230" t="n">
         <v>2</v>
@@ -36951,27 +36401,21 @@
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL231" t="inlineStr">
-        <is>
-          <t>Methanol</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL231" t="inlineStr"/>
       <c r="AM231" t="n">
         <v>2.5</v>
       </c>
-      <c r="AN231" t="n">
-        <v>1</v>
-      </c>
+      <c r="AN231" t="inlineStr"/>
       <c r="AO231" t="inlineStr">
         <is>
           <t>97:3</t>
         </is>
       </c>
       <c r="AP231" t="n">
-        <v>1.33</v>
+        <v>0.4433333333333334</v>
       </c>
       <c r="AQ231" t="n">
         <v>633</v>
@@ -36983,13 +36427,13 @@
         <v>3</v>
       </c>
       <c r="AT231" t="n">
-        <v>0.3064103049153603</v>
+        <v>0.1018814263843573</v>
       </c>
       <c r="AU231" t="n">
-        <v>0.7660257622884007</v>
+        <v>0.2547035659608932</v>
       </c>
       <c r="AV231" t="n">
-        <v>5.132311325271301</v>
+        <v>1.706493515652707</v>
       </c>
       <c r="AW231" t="n">
         <v>2</v>
@@ -37113,14 +36557,10 @@
       </c>
       <c r="AK232" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL232" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL232" t="inlineStr"/>
       <c r="AM232" t="n">
         <v>3.5</v>
       </c>
@@ -37263,14 +36703,10 @@
       </c>
       <c r="AK233" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL233" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL233" t="inlineStr"/>
       <c r="AM233" t="n">
         <v>3.5</v>
       </c>
@@ -37413,14 +36849,10 @@
       </c>
       <c r="AK234" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL234" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL234" t="inlineStr"/>
       <c r="AM234" t="n">
         <v>3.5</v>
       </c>
@@ -37563,14 +36995,10 @@
       </c>
       <c r="AK235" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL235" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL235" t="inlineStr"/>
       <c r="AM235" t="n">
         <v>3.5</v>
       </c>
@@ -37713,14 +37141,10 @@
       </c>
       <c r="AK236" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL236" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL236" t="inlineStr"/>
       <c r="AM236" t="n">
         <v>3.5</v>
       </c>
@@ -37863,14 +37287,10 @@
       </c>
       <c r="AK237" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL237" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL237" t="inlineStr"/>
       <c r="AM237" t="n">
         <v>3.5</v>
       </c>
@@ -38013,14 +37433,10 @@
       </c>
       <c r="AK238" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL238" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL238" t="inlineStr"/>
       <c r="AM238" t="n">
         <v>3.5</v>
       </c>
@@ -38163,14 +37579,10 @@
       </c>
       <c r="AK239" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL239" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL239" t="inlineStr"/>
       <c r="AM239" t="n">
         <v>3.5</v>
       </c>
@@ -38313,14 +37725,10 @@
       </c>
       <c r="AK240" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL240" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL240" t="inlineStr"/>
       <c r="AM240" t="n">
         <v>5</v>
       </c>
@@ -38473,14 +37881,10 @@
       </c>
       <c r="AK241" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL241" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL241" t="inlineStr"/>
       <c r="AM241" t="n">
         <v>5</v>
       </c>
@@ -38631,14 +38035,10 @@
       </c>
       <c r="AK242" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL242" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL242" t="inlineStr"/>
       <c r="AM242" t="n">
         <v>2.5</v>
       </c>
@@ -38791,14 +38191,10 @@
       </c>
       <c r="AK243" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL243" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL243" t="inlineStr"/>
       <c r="AM243" t="n">
         <v>5</v>
       </c>
@@ -38951,14 +38347,10 @@
       </c>
       <c r="AK244" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL244" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL244" t="inlineStr"/>
       <c r="AM244" t="n">
         <v>5</v>
       </c>
@@ -39111,14 +38503,10 @@
       </c>
       <c r="AK245" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL245" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL245" t="inlineStr"/>
       <c r="AM245" t="n">
         <v>5</v>
       </c>
@@ -39271,14 +38659,10 @@
       </c>
       <c r="AK246" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL246" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL246" t="inlineStr"/>
       <c r="AM246" t="n">
         <v>5</v>
       </c>
@@ -39431,14 +38815,10 @@
       </c>
       <c r="AK247" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL247" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL247" t="inlineStr"/>
       <c r="AM247" t="n">
         <v>5</v>
       </c>
@@ -39591,14 +38971,10 @@
       </c>
       <c r="AK248" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL248" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL248" t="inlineStr"/>
       <c r="AM248" t="n">
         <v>5</v>
       </c>
@@ -39751,14 +39127,10 @@
       </c>
       <c r="AK249" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL249" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL249" t="inlineStr"/>
       <c r="AM249" t="n">
         <v>5</v>
       </c>
@@ -39911,14 +39283,10 @@
       </c>
       <c r="AK250" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL250" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL250" t="inlineStr"/>
       <c r="AM250" t="n">
         <v>5</v>
       </c>
@@ -40071,14 +39439,10 @@
       </c>
       <c r="AK251" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL251" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL251" t="inlineStr"/>
       <c r="AM251" t="n">
         <v>5</v>
       </c>
@@ -40231,14 +39595,10 @@
       </c>
       <c r="AK252" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL252" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL252" t="inlineStr"/>
       <c r="AM252" t="n">
         <v>5</v>
       </c>
@@ -40391,14 +39751,10 @@
       </c>
       <c r="AK253" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL253" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL253" t="inlineStr"/>
       <c r="AM253" t="n">
         <v>5</v>
       </c>
@@ -40551,14 +39907,10 @@
       </c>
       <c r="AK254" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL254" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL254" t="inlineStr"/>
       <c r="AM254" t="n">
         <v>5</v>
       </c>
@@ -40711,14 +40063,10 @@
       </c>
       <c r="AK255" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL255" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL255" t="inlineStr"/>
       <c r="AM255" t="n">
         <v>1</v>
       </c>
@@ -40863,14 +40211,10 @@
       </c>
       <c r="AK256" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL256" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL256" t="inlineStr"/>
       <c r="AM256" t="n">
         <v>1</v>
       </c>
@@ -41015,14 +40359,10 @@
       </c>
       <c r="AK257" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL257" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL257" t="inlineStr"/>
       <c r="AM257" t="n">
         <v>1</v>
       </c>
@@ -41167,14 +40507,10 @@
       </c>
       <c r="AK258" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL258" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL258" t="inlineStr"/>
       <c r="AM258" t="n">
         <v>1</v>
       </c>
@@ -41317,14 +40653,10 @@
       </c>
       <c r="AK259" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL259" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL259" t="inlineStr"/>
       <c r="AM259" t="n">
         <v>5</v>
       </c>
@@ -41477,14 +40809,10 @@
       </c>
       <c r="AK260" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL260" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL260" t="inlineStr"/>
       <c r="AM260" t="n">
         <v>3</v>
       </c>
@@ -41637,14 +40965,10 @@
       </c>
       <c r="AK261" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL261" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL261" t="inlineStr"/>
       <c r="AM261" t="n">
         <v>3</v>
       </c>
@@ -41795,14 +41119,10 @@
       </c>
       <c r="AK262" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL262" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL262" t="inlineStr"/>
       <c r="AM262" t="n">
         <v>3</v>
       </c>
@@ -41956,11 +41276,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL263" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL263" t="inlineStr"/>
       <c r="AM263" t="n">
         <v>2.5</v>
       </c>
@@ -42115,14 +41431,10 @@
       </c>
       <c r="AK264" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL264" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL264" t="inlineStr"/>
       <c r="AM264" t="n">
         <v>3</v>
       </c>
@@ -42275,14 +41587,10 @@
       </c>
       <c r="AK265" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL265" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL265" t="inlineStr"/>
       <c r="AM265" t="n">
         <v>3</v>
       </c>
@@ -42435,14 +41743,10 @@
       </c>
       <c r="AK266" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL266" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL266" t="inlineStr"/>
       <c r="AM266" t="n">
         <v>3</v>
       </c>
@@ -42595,14 +41899,10 @@
       </c>
       <c r="AK267" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL267" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL267" t="inlineStr"/>
       <c r="AM267" t="n">
         <v>2.5</v>
       </c>
@@ -42753,14 +42053,10 @@
       </c>
       <c r="AK268" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL268" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL268" t="inlineStr"/>
       <c r="AM268" t="n">
         <v>10</v>
       </c>
@@ -42913,14 +42209,10 @@
       </c>
       <c r="AK269" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL269" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL269" t="inlineStr"/>
       <c r="AM269" t="n">
         <v>10</v>
       </c>
@@ -43073,14 +42365,10 @@
       </c>
       <c r="AK270" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL270" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL270" t="inlineStr"/>
       <c r="AM270" t="n">
         <v>10</v>
       </c>
@@ -43233,14 +42521,10 @@
       </c>
       <c r="AK271" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL271" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL271" t="inlineStr"/>
       <c r="AM271" t="n">
         <v>7.5</v>
       </c>
@@ -43393,14 +42677,10 @@
       </c>
       <c r="AK272" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL272" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL272" t="inlineStr"/>
       <c r="AM272" t="n">
         <v>5</v>
       </c>
@@ -43553,14 +42833,10 @@
       </c>
       <c r="AK273" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL273" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL273" t="inlineStr"/>
       <c r="AM273" t="n">
         <v>1</v>
       </c>
@@ -43705,14 +42981,10 @@
       </c>
       <c r="AK274" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL274" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL274" t="inlineStr"/>
       <c r="AM274" t="n">
         <v>1</v>
       </c>
@@ -43857,14 +43129,10 @@
       </c>
       <c r="AK275" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL275" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL275" t="inlineStr"/>
       <c r="AM275" t="n">
         <v>1</v>
       </c>
@@ -44009,14 +43277,10 @@
       </c>
       <c r="AK276" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL276" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL276" t="inlineStr"/>
       <c r="AM276" t="n">
         <v>1</v>
       </c>
@@ -44161,14 +43425,10 @@
       </c>
       <c r="AK277" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL277" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL277" t="inlineStr"/>
       <c r="AM277" t="n">
         <v>1</v>
       </c>
@@ -44313,14 +43573,10 @@
       </c>
       <c r="AK278" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL278" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL278" t="inlineStr"/>
       <c r="AM278" t="n">
         <v>3</v>
       </c>
@@ -44471,14 +43727,10 @@
       </c>
       <c r="AK279" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL279" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL279" t="inlineStr"/>
       <c r="AM279" t="n">
         <v>3</v>
       </c>
@@ -44629,14 +43881,10 @@
       </c>
       <c r="AK280" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL280" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL280" t="inlineStr"/>
       <c r="AM280" t="n">
         <v>3</v>
       </c>
@@ -44789,14 +44037,10 @@
       </c>
       <c r="AK281" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL281" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL281" t="inlineStr"/>
       <c r="AM281" t="n">
         <v>3</v>
       </c>
@@ -44949,14 +44193,10 @@
       </c>
       <c r="AK282" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL282" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL282" t="inlineStr"/>
       <c r="AM282" t="n">
         <v>3</v>
       </c>
@@ -45109,14 +44349,10 @@
       </c>
       <c r="AK283" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL283" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL283" t="inlineStr"/>
       <c r="AM283" t="n">
         <v>3</v>
       </c>
@@ -45272,11 +44508,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL284" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL284" t="inlineStr"/>
       <c r="AM284" t="n">
         <v>1.6</v>
       </c>
@@ -45422,11 +44654,7 @@
           <t>DMM</t>
         </is>
       </c>
-      <c r="AL285" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="AL285" t="inlineStr"/>
       <c r="AM285" t="n">
         <v>1.6</v>
       </c>
@@ -45569,14 +44797,10 @@
       </c>
       <c r="AK286" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL286" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL286" t="inlineStr"/>
       <c r="AM286" t="n">
         <v>3</v>
       </c>
@@ -45729,14 +44953,10 @@
       </c>
       <c r="AK287" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL287" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL287" t="inlineStr"/>
       <c r="AM287" t="n">
         <v>3</v>
       </c>
@@ -45889,14 +45109,10 @@
       </c>
       <c r="AK288" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL288" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL288" t="inlineStr"/>
       <c r="AM288" t="n">
         <v>3</v>
       </c>
@@ -46049,14 +45265,10 @@
       </c>
       <c r="AK289" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL289" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL289" t="inlineStr"/>
       <c r="AM289" t="n">
         <v>3</v>
       </c>
@@ -46209,14 +45421,10 @@
       </c>
       <c r="AK290" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL290" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL290" t="inlineStr"/>
       <c r="AM290" t="n">
         <v>3</v>
       </c>
@@ -46369,14 +45577,10 @@
       </c>
       <c r="AK291" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL291" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL291" t="inlineStr"/>
       <c r="AM291" t="n">
         <v>2.5</v>
       </c>
@@ -46529,14 +45733,10 @@
       </c>
       <c r="AK292" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL292" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL292" t="inlineStr"/>
       <c r="AM292" t="n">
         <v>2.5</v>
       </c>
@@ -46689,14 +45889,10 @@
       </c>
       <c r="AK293" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL293" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL293" t="inlineStr"/>
       <c r="AM293" t="n">
         <v>2.5</v>
       </c>
@@ -46849,14 +46045,10 @@
       </c>
       <c r="AK294" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL294" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL294" t="inlineStr"/>
       <c r="AM294" t="n">
         <v>2.5</v>
       </c>
@@ -47009,14 +46201,10 @@
       </c>
       <c r="AK295" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL295" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL295" t="inlineStr"/>
       <c r="AM295" t="n">
         <v>1</v>
       </c>
@@ -47161,14 +46349,10 @@
       </c>
       <c r="AK296" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL296" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL296" t="inlineStr"/>
       <c r="AM296" t="n">
         <v>2.5</v>
       </c>
@@ -47321,14 +46505,10 @@
       </c>
       <c r="AK297" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL297" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL297" t="inlineStr"/>
       <c r="AM297" t="n">
         <v>2.5</v>
       </c>
@@ -47481,14 +46661,10 @@
       </c>
       <c r="AK298" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL298" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL298" t="inlineStr"/>
       <c r="AM298" t="n">
         <v>2.5</v>
       </c>
@@ -47641,14 +46817,10 @@
       </c>
       <c r="AK299" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL299" t="inlineStr">
-        <is>
-          <t>Commercial formalin</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL299" t="inlineStr"/>
       <c r="AM299" t="n">
         <v>2.5</v>
       </c>
@@ -47801,14 +46973,10 @@
       </c>
       <c r="AK300" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL300" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL300" t="inlineStr"/>
       <c r="AM300" t="n">
         <v>5</v>
       </c>
@@ -47961,14 +47129,10 @@
       </c>
       <c r="AK301" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL301" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL301" t="inlineStr"/>
       <c r="AM301" t="n">
         <v>1</v>
       </c>
@@ -48113,14 +47277,10 @@
       </c>
       <c r="AK302" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL302" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL302" t="inlineStr"/>
       <c r="AM302" t="n">
         <v>3</v>
       </c>
@@ -48275,14 +47435,10 @@
       </c>
       <c r="AK303" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL303" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL303" t="inlineStr"/>
       <c r="AM303" t="n">
         <v>5</v>
       </c>
@@ -48435,14 +47591,10 @@
       </c>
       <c r="AK304" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL304" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL304" t="inlineStr"/>
       <c r="AM304" t="n">
         <v>3</v>
       </c>
@@ -48595,14 +47747,10 @@
       </c>
       <c r="AK305" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL305" t="inlineStr">
-        <is>
-          <t>Paraformaldehyde</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL305" t="inlineStr"/>
       <c r="AM305" t="n">
         <v>1</v>
       </c>
@@ -48747,14 +47895,10 @@
       </c>
       <c r="AK306" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL306" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL306" t="inlineStr"/>
       <c r="AM306" t="n">
         <v>3</v>
       </c>
@@ -48907,14 +48051,10 @@
       </c>
       <c r="AK307" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL307" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL307" t="inlineStr"/>
       <c r="AM307" t="n">
         <v>5</v>
       </c>
@@ -49067,14 +48207,10 @@
       </c>
       <c r="AK308" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL308" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL308" t="inlineStr"/>
       <c r="AM308" t="n">
         <v>5</v>
       </c>
@@ -49227,14 +48363,10 @@
       </c>
       <c r="AK309" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL309" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL309" t="inlineStr"/>
       <c r="AM309" t="n">
         <v>5</v>
       </c>
@@ -49387,14 +48519,10 @@
       </c>
       <c r="AK310" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL310" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL310" t="inlineStr"/>
       <c r="AM310" t="n">
         <v>5</v>
       </c>
@@ -49547,14 +48675,10 @@
       </c>
       <c r="AK311" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL311" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL311" t="inlineStr"/>
       <c r="AM311" t="n">
         <v>5</v>
       </c>
@@ -49567,11 +48691,7 @@
       <c r="AP311" t="n">
         <v>1.2</v>
       </c>
-      <c r="AQ311" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
+      <c r="AQ311" t="inlineStr"/>
       <c r="AR311" t="n">
         <v>1</v>
       </c>
@@ -49709,14 +48829,10 @@
       </c>
       <c r="AK312" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL312" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL312" t="inlineStr"/>
       <c r="AM312" t="n">
         <v>5</v>
       </c>
@@ -49729,11 +48845,7 @@
       <c r="AP312" t="n">
         <v>1.2</v>
       </c>
-      <c r="AQ312" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
+      <c r="AQ312" t="inlineStr"/>
       <c r="AR312" t="n">
         <v>1</v>
       </c>
@@ -49871,14 +48983,10 @@
       </c>
       <c r="AK313" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL313" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL313" t="inlineStr"/>
       <c r="AM313" t="n">
         <v>5</v>
       </c>
@@ -49891,11 +48999,7 @@
       <c r="AP313" t="n">
         <v>1.2</v>
       </c>
-      <c r="AQ313" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
+      <c r="AQ313" t="inlineStr"/>
       <c r="AR313" t="n">
         <v>1</v>
       </c>
@@ -50033,14 +49137,10 @@
       </c>
       <c r="AK314" t="inlineStr">
         <is>
-          <t>Trioxane</t>
-        </is>
-      </c>
-      <c r="AL314" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>TRX</t>
+        </is>
+      </c>
+      <c r="AL314" t="inlineStr"/>
       <c r="AM314" t="n">
         <v>5</v>
       </c>
@@ -50193,14 +49293,10 @@
       </c>
       <c r="AK315" t="inlineStr">
         <is>
-          <t>Formalin</t>
-        </is>
-      </c>
-      <c r="AL315" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>FORM</t>
+        </is>
+      </c>
+      <c r="AL315" t="inlineStr"/>
       <c r="AM315" t="n">
         <v>5</v>
       </c>

--- a/data/data_clustered.xlsx
+++ b/data/data_clustered.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX315"/>
+  <dimension ref="A1:AY315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,10 +671,15 @@
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
           <t>Cluster_n</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>Cluster title</t>
         </is>
@@ -827,10 +832,15 @@
       <c r="AV2" t="n">
         <v>0.5955842332613392</v>
       </c>
-      <c r="AW2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY2" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -977,10 +987,15 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>10.1039/C6CY00620E</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -1127,10 +1142,15 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>10.1039/C6CY00620E</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -1277,10 +1297,15 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>10.1039/C6CY00620E</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -1439,10 +1464,15 @@
       <c r="AV6" t="n">
         <v>0.6996076572598475</v>
       </c>
-      <c r="AW6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.2c03415</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -1595,10 +1625,15 @@
       <c r="AV7" t="n">
         <v>0.771274570811601</v>
       </c>
-      <c r="AW7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>10.1039/D2RA06960A</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -1751,10 +1786,15 @@
       <c r="AV8" t="n">
         <v>0.6732217411871608</v>
       </c>
-      <c r="AW8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>10.1039/D2RA06960A</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -1913,10 +1953,15 @@
       <c r="AV9" t="n">
         <v>13.29038020513888</v>
       </c>
-      <c r="AW9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-017-2014-8</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -2075,10 +2120,15 @@
       <c r="AV10" t="n">
         <v>3.236708989464488</v>
       </c>
-      <c r="AW10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-017-2014-8</t>
+        </is>
+      </c>
+      <c r="AX10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -2237,10 +2287,15 @@
       <c r="AV11" t="n">
         <v>6.477051706276816</v>
       </c>
-      <c r="AW11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-017-2014-8</t>
+        </is>
+      </c>
+      <c r="AX11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -2399,10 +2454,15 @@
       <c r="AV12" t="n">
         <v>6.838899172791308</v>
       </c>
-      <c r="AW12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-017-2014-8</t>
+        </is>
+      </c>
+      <c r="AX12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -2561,10 +2621,15 @@
       <c r="AV13" t="n">
         <v>11.07093542974365</v>
       </c>
-      <c r="AW13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX13" t="inlineStr">
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-017-2014-8</t>
+        </is>
+      </c>
+      <c r="AX13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY13" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -2723,10 +2788,15 @@
       <c r="AV14" t="n">
         <v>12.03544330602205</v>
       </c>
-      <c r="AW14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-017-2014-8</t>
+        </is>
+      </c>
+      <c r="AX14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY14" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -2885,10 +2955,15 @@
       <c r="AV15" t="n">
         <v>12.52299082227291</v>
       </c>
-      <c r="AW15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-017-2014-8</t>
+        </is>
+      </c>
+      <c r="AX15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY15" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -3047,10 +3122,15 @@
       <c r="AV16" t="n">
         <v>13.17401120834511</v>
       </c>
-      <c r="AW16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-017-2014-8</t>
+        </is>
+      </c>
+      <c r="AX16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY16" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -3209,10 +3289,15 @@
       <c r="AV17" t="n">
         <v>14.5255783384156</v>
       </c>
-      <c r="AW17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-017-2014-8</t>
+        </is>
+      </c>
+      <c r="AX17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY17" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -3371,10 +3456,15 @@
       <c r="AV18" t="n">
         <v>16.17609804930094</v>
       </c>
-      <c r="AW18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-017-2014-8</t>
+        </is>
+      </c>
+      <c r="AX18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY18" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -3531,10 +3621,15 @@
       <c r="AV19" t="n">
         <v>17.82231112036662</v>
       </c>
-      <c r="AW19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX19" t="inlineStr">
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-017-2014-8</t>
+        </is>
+      </c>
+      <c r="AX19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY19" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -3691,10 +3786,15 @@
       <c r="AV20" t="n">
         <v>13.33927851142462</v>
       </c>
-      <c r="AW20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX20" t="inlineStr">
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>10.1039/C7RA10008F</t>
+        </is>
+      </c>
+      <c r="AX20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY20" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -3851,10 +3951,15 @@
       <c r="AV21" t="n">
         <v>16.22015138578957</v>
       </c>
-      <c r="AW21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX21" t="inlineStr">
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>10.1039/C7RA10008F</t>
+        </is>
+      </c>
+      <c r="AX21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY21" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -4011,10 +4116,15 @@
       <c r="AV22" t="n">
         <v>11.86156272330321</v>
       </c>
-      <c r="AW22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>10.1039/C7RA10008F</t>
+        </is>
+      </c>
+      <c r="AX22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY22" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -4171,10 +4281,15 @@
       <c r="AV23" t="n">
         <v>14.56074923027617</v>
       </c>
-      <c r="AW23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX23" t="inlineStr">
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>10.1039/C7RA10008F</t>
+        </is>
+      </c>
+      <c r="AX23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY23" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -4331,10 +4446,15 @@
       <c r="AV24" t="n">
         <v>15.50390335078208</v>
       </c>
-      <c r="AW24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX24" t="inlineStr">
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>10.1039/C7RA10008F</t>
+        </is>
+      </c>
+      <c r="AX24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY24" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -4491,10 +4611,15 @@
       <c r="AV25" t="n">
         <v>16.61322199099661</v>
       </c>
-      <c r="AW25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX25" t="inlineStr">
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>10.1039/C7RA10008F</t>
+        </is>
+      </c>
+      <c r="AX25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY25" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -4651,10 +4776,15 @@
       <c r="AV26" t="n">
         <v>16.94034717396508</v>
       </c>
-      <c r="AW26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX26" t="inlineStr">
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>10.1039/C7RA10008F</t>
+        </is>
+      </c>
+      <c r="AX26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY26" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -4813,10 +4943,15 @@
       <c r="AV27" t="n">
         <v>12.9917380612777</v>
       </c>
-      <c r="AW27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX27" t="inlineStr">
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2535-9</t>
+        </is>
+      </c>
+      <c r="AX27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY27" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -4975,10 +5110,15 @@
       <c r="AV28" t="n">
         <v>11.9741669991213</v>
       </c>
-      <c r="AW28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX28" t="inlineStr">
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2535-9</t>
+        </is>
+      </c>
+      <c r="AX28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY28" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -5137,10 +5277,15 @@
       <c r="AV29" t="n">
         <v>16.57934578273182</v>
       </c>
-      <c r="AW29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX29" t="inlineStr">
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2535-9</t>
+        </is>
+      </c>
+      <c r="AX29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY29" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -5299,10 +5444,15 @@
       <c r="AV30" t="n">
         <v>17.10723081280191</v>
       </c>
-      <c r="AW30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX30" t="inlineStr">
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2535-9</t>
+        </is>
+      </c>
+      <c r="AX30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY30" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -5447,10 +5597,15 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AU31" t="inlineStr"/>
       <c r="AV31" t="inlineStr"/>
-      <c r="AW31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX31" t="inlineStr">
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b02522</t>
+        </is>
+      </c>
+      <c r="AX31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY31" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -5603,10 +5758,15 @@
       <c r="AV32" t="n">
         <v>1.037342752224622</v>
       </c>
-      <c r="AW32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX32" t="inlineStr">
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
+      <c r="AX32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY32" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -5759,10 +5919,15 @@
       <c r="AV33" t="n">
         <v>0.6083303095464363</v>
       </c>
-      <c r="AW33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX33" t="inlineStr">
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
+      <c r="AX33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY33" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -5915,10 +6080,15 @@
       <c r="AV34" t="n">
         <v>1.035357229892009</v>
       </c>
-      <c r="AW34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX34" t="inlineStr">
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
+      <c r="AX34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY34" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -6075,10 +6245,15 @@
       <c r="AV35" t="n">
         <v>2.264403873433229</v>
       </c>
-      <c r="AW35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX35" t="inlineStr">
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>10.1016/j.cjche.2021.11.025</t>
+        </is>
+      </c>
+      <c r="AX35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY35" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -6235,10 +6410,15 @@
       <c r="AV36" t="n">
         <v>2.403258827936211</v>
       </c>
-      <c r="AW36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX36" t="inlineStr">
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>10.1016/j.cjche.2021.11.025</t>
+        </is>
+      </c>
+      <c r="AX36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY36" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -6395,10 +6575,15 @@
       <c r="AV37" t="n">
         <v>1.506042198840025</v>
       </c>
-      <c r="AW37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX37" t="inlineStr">
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>10.1016/j.cjche.2021.11.025</t>
+        </is>
+      </c>
+      <c r="AX37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY37" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -6555,10 +6740,15 @@
       <c r="AV38" t="n">
         <v>1.185607688448531</v>
       </c>
-      <c r="AW38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX38" t="inlineStr">
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>10.1016/j.cjche.2021.11.025</t>
+        </is>
+      </c>
+      <c r="AX38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY38" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -6703,10 +6893,15 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AU39" t="inlineStr"/>
       <c r="AV39" t="inlineStr"/>
-      <c r="AW39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX39" t="inlineStr">
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>10.1016/S1872‐2067(18)63069‐4</t>
+        </is>
+      </c>
+      <c r="AX39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY39" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -6865,10 +7060,15 @@
       <c r="AV40" t="n">
         <v>0.3794963157532329</v>
       </c>
-      <c r="AW40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX40" t="inlineStr">
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.1c04460</t>
+        </is>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -7025,10 +7225,15 @@
       <c r="AV41" t="n">
         <v>0</v>
       </c>
-      <c r="AW41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX41" t="inlineStr">
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>10.1016/j.cjche.2021.11.025</t>
+        </is>
+      </c>
+      <c r="AX41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY41" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -7171,10 +7376,15 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AU42" t="inlineStr"/>
       <c r="AV42" t="inlineStr"/>
-      <c r="AW42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX42" t="inlineStr">
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
+      <c r="AX42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY42" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -7327,10 +7537,15 @@
       <c r="AV43" t="n">
         <v>3.702138292163938</v>
       </c>
-      <c r="AW43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX43" t="inlineStr">
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>10.1002/jctb.7032</t>
+        </is>
+      </c>
+      <c r="AX43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY43" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -7483,10 +7698,15 @@
       <c r="AV44" t="n">
         <v>5.624765755944122</v>
       </c>
-      <c r="AW44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX44" t="inlineStr">
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>10.1002/jctb.7032</t>
+        </is>
+      </c>
+      <c r="AX44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY44" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -7639,10 +7859,15 @@
       <c r="AV45" t="n">
         <v>5.479437961698586</v>
       </c>
-      <c r="AW45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX45" t="inlineStr">
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>10.1002/jctb.7032</t>
+        </is>
+      </c>
+      <c r="AX45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY45" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -7795,10 +8020,15 @@
       <c r="AV46" t="n">
         <v>4.441654779239522</v>
       </c>
-      <c r="AW46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX46" t="inlineStr">
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>10.1002/jctb.7032</t>
+        </is>
+      </c>
+      <c r="AX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY46" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -7951,10 +8181,15 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AU47" t="inlineStr"/>
       <c r="AV47" t="inlineStr"/>
-      <c r="AW47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX47" t="inlineStr">
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.1c03082</t>
+        </is>
+      </c>
+      <c r="AX47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY47" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -8097,10 +8332,15 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AU48" t="inlineStr"/>
       <c r="AV48" t="inlineStr"/>
-      <c r="AW48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX48" t="inlineStr">
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
+      <c r="AX48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY48" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -8259,10 +8499,15 @@
       <c r="AV49" t="n">
         <v>0.2861124139451171</v>
       </c>
-      <c r="AW49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX49" t="inlineStr">
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2023.145655</t>
+        </is>
+      </c>
+      <c r="AX49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY49" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -8415,10 +8660,15 @@
       <c r="AV50" t="n">
         <v>0.2759276079913607</v>
       </c>
-      <c r="AW50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX50" t="inlineStr">
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
+      <c r="AX50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY50" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -8571,10 +8821,15 @@
       <c r="AV51" t="n">
         <v>0.08603980431965444</v>
       </c>
-      <c r="AW51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX51" t="inlineStr">
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
+      <c r="AX51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY51" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -8727,10 +8982,15 @@
       <c r="AV52" t="n">
         <v>0.2703290256155508</v>
       </c>
-      <c r="AW52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX52" t="inlineStr">
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
+      <c r="AX52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY52" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -8883,10 +9143,15 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AU53" t="inlineStr"/>
       <c r="AV53" t="inlineStr"/>
-      <c r="AW53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX53" t="inlineStr">
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiec.2016.11.002</t>
+        </is>
+      </c>
+      <c r="AX53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY53" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -9039,10 +9304,15 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AU54" t="inlineStr"/>
       <c r="AV54" t="inlineStr"/>
-      <c r="AW54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX54" t="inlineStr">
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiec.2016.11.002</t>
+        </is>
+      </c>
+      <c r="AX54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY54" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -9195,10 +9465,15 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AU55" t="inlineStr"/>
       <c r="AV55" t="inlineStr"/>
-      <c r="AW55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX55" t="inlineStr">
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiec.2016.11.002</t>
+        </is>
+      </c>
+      <c r="AX55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY55" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -9357,10 +9632,15 @@
       <c r="AV56" t="n">
         <v>1.463177140327438</v>
       </c>
-      <c r="AW56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX56" t="inlineStr">
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.2c03415</t>
+        </is>
+      </c>
+      <c r="AX56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY56" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -9519,10 +9799,15 @@
       <c r="AV57" t="n">
         <v>3.419587658065798</v>
       </c>
-      <c r="AW57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX57" t="inlineStr">
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.2c03415</t>
+        </is>
+      </c>
+      <c r="AX57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY57" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -9681,10 +9966,15 @@
       <c r="AV58" t="n">
         <v>6.069304012704706</v>
       </c>
-      <c r="AW58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX58" t="inlineStr">
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.2c03415</t>
+        </is>
+      </c>
+      <c r="AX58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY58" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -9841,10 +10131,15 @@
       <c r="AV59" t="n">
         <v>0.3024225830464325</v>
       </c>
-      <c r="AW59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX59" t="inlineStr">
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>10.4028/www.scientific.net/AMR.629.376</t>
+        </is>
+      </c>
+      <c r="AX59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY59" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -10001,10 +10296,15 @@
       <c r="AV60" t="n">
         <v>1.445984926025873</v>
       </c>
-      <c r="AW60" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX60" t="inlineStr">
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>10.4028/www.scientific.net/AMR.629.376</t>
+        </is>
+      </c>
+      <c r="AX60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY60" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -10161,10 +10461,15 @@
       <c r="AV61" t="n">
         <v>1.77628058993208</v>
       </c>
-      <c r="AW61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX61" t="inlineStr">
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>10.4028/www.scientific.net/AMR.629.376</t>
+        </is>
+      </c>
+      <c r="AX61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY61" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -10321,10 +10626,15 @@
       <c r="AV62" t="n">
         <v>0.2558602546059374</v>
       </c>
-      <c r="AW62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX62" t="inlineStr">
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>10.1556/JFC-D-14-00035</t>
+        </is>
+      </c>
+      <c r="AX62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY62" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -10483,10 +10793,15 @@
       <c r="AV63" t="n">
         <v>3.634130663173834</v>
       </c>
-      <c r="AW63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX63" t="inlineStr">
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>10.1016/j.cattod.2020.06.026</t>
+        </is>
+      </c>
+      <c r="AX63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY63" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -10645,10 +10960,15 @@
       <c r="AV64" t="n">
         <v>2.371075264188601</v>
       </c>
-      <c r="AW64" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX64" t="inlineStr">
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>10.1016/j.cattod.2020.06.026</t>
+        </is>
+      </c>
+      <c r="AX64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY64" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -10807,10 +11127,15 @@
       <c r="AV65" t="n">
         <v>3.786562125771817</v>
       </c>
-      <c r="AW65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX65" t="inlineStr">
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>10.1016/j.cattod.2020.06.026</t>
+        </is>
+      </c>
+      <c r="AX65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY65" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -10969,10 +11294,15 @@
       <c r="AV66" t="n">
         <v>1.891540793050767</v>
       </c>
-      <c r="AW66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX66" t="inlineStr">
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>10.1016/j.cattod.2020.06.026</t>
+        </is>
+      </c>
+      <c r="AX66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY66" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -11131,10 +11461,15 @@
       <c r="AV67" t="n">
         <v>5.376879068075143</v>
       </c>
-      <c r="AW67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX67" t="inlineStr">
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2023.145655</t>
+        </is>
+      </c>
+      <c r="AX67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY67" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -11293,10 +11628,15 @@
       <c r="AV68" t="n">
         <v>7.903561347560993</v>
       </c>
-      <c r="AW68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX68" t="inlineStr">
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2023.145655</t>
+        </is>
+      </c>
+      <c r="AX68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY68" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -11455,10 +11795,15 @@
       <c r="AV69" t="n">
         <v>13.45604648323464</v>
       </c>
-      <c r="AW69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX69" t="inlineStr">
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>10.1007/s11144-018-1419-8</t>
+        </is>
+      </c>
+      <c r="AX69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY69" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -11611,10 +11956,15 @@
       <c r="AV70" t="n">
         <v>0.05598754483801297</v>
       </c>
-      <c r="AW70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX70" t="inlineStr">
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
+      <c r="AX70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY70" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -11767,10 +12117,15 @@
       <c r="AV71" t="n">
         <v>0.150405173650108</v>
       </c>
-      <c r="AW71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX71" t="inlineStr">
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
+      <c r="AX71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY71" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -11919,10 +12274,15 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AU72" t="inlineStr"/>
       <c r="AV72" t="inlineStr"/>
-      <c r="AW72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX72" t="inlineStr">
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2609-8</t>
+        </is>
+      </c>
+      <c r="AX72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY72" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -12071,10 +12431,15 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AU73" t="inlineStr"/>
       <c r="AV73" t="inlineStr"/>
-      <c r="AW73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX73" t="inlineStr">
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2609-8</t>
+        </is>
+      </c>
+      <c r="AX73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY73" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -12223,10 +12588,15 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AU74" t="inlineStr"/>
       <c r="AV74" t="inlineStr"/>
-      <c r="AW74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX74" t="inlineStr">
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2609-8</t>
+        </is>
+      </c>
+      <c r="AX74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY74" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -12379,10 +12749,15 @@
       <c r="AV75" t="n">
         <v>21.21964717062635</v>
       </c>
-      <c r="AW75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX75" t="inlineStr">
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiec.2014.11.014</t>
+        </is>
+      </c>
+      <c r="AX75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY75" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -12535,10 +12910,15 @@
       <c r="AV76" t="n">
         <v>13.61464794816415</v>
       </c>
-      <c r="AW76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX76" t="inlineStr">
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiec.2014.11.014</t>
+        </is>
+      </c>
+      <c r="AX76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY76" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -12697,10 +13077,15 @@
       <c r="AV77" t="n">
         <v>10.39883272224373</v>
       </c>
-      <c r="AW77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX77" t="inlineStr">
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>10.1007/s11144-018-1419-8</t>
+        </is>
+      </c>
+      <c r="AX77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY77" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -12853,10 +13238,15 @@
       <c r="AV78" t="n">
         <v>0.04646637978401728</v>
       </c>
-      <c r="AW78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX78" t="inlineStr">
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
+      <c r="AX78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY78" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -13009,10 +13399,15 @@
       <c r="AV79" t="n">
         <v>0.2214445889416847</v>
       </c>
-      <c r="AW79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX79" t="inlineStr">
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
+      <c r="AX79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY79" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -13161,10 +13556,15 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AU80" t="inlineStr"/>
       <c r="AV80" t="inlineStr"/>
-      <c r="AW80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX80" t="inlineStr">
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b02841</t>
+        </is>
+      </c>
+      <c r="AX80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY80" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -13313,10 +13713,15 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AU81" t="inlineStr"/>
       <c r="AV81" t="inlineStr"/>
-      <c r="AW81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX81" t="inlineStr">
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b02841</t>
+        </is>
+      </c>
+      <c r="AX81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY81" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -13475,10 +13880,15 @@
       <c r="AV82" t="n">
         <v>1.495361048493642</v>
       </c>
-      <c r="AW82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX82" t="inlineStr">
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.1c04460</t>
+        </is>
+      </c>
+      <c r="AX82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY82" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -13637,10 +14047,15 @@
       <c r="AV83" t="n">
         <v>1.64176449330127</v>
       </c>
-      <c r="AW83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX83" t="inlineStr">
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.1c04460</t>
+        </is>
+      </c>
+      <c r="AX83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY83" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -13799,10 +14214,15 @@
       <c r="AV84" t="n">
         <v>1.091613565400359</v>
       </c>
-      <c r="AW84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX84" t="inlineStr">
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.2c00444</t>
+        </is>
+      </c>
+      <c r="AX84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY84" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -13961,10 +14381,15 @@
       <c r="AV85" t="n">
         <v>2.13088949410344</v>
       </c>
-      <c r="AW85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX85" t="inlineStr">
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.2c00444</t>
+        </is>
+      </c>
+      <c r="AX85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY85" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -14123,10 +14548,15 @@
       <c r="AV86" t="n">
         <v>3.753356231719042</v>
       </c>
-      <c r="AW86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX86" t="inlineStr">
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.2c00444</t>
+        </is>
+      </c>
+      <c r="AX86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY86" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -14285,10 +14715,15 @@
       <c r="AV87" t="n">
         <v>2.139319741550428</v>
       </c>
-      <c r="AW87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX87" t="inlineStr">
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>10.1080/00219592.2023.2300818</t>
+        </is>
+      </c>
+      <c r="AX87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY87" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -14447,10 +14882,15 @@
       <c r="AV88" t="n">
         <v>3.357085553868227</v>
       </c>
-      <c r="AW88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX88" t="inlineStr">
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.4c00771</t>
+        </is>
+      </c>
+      <c r="AX88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY88" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -14609,10 +15049,15 @@
       <c r="AV89" t="n">
         <v>1.735801660800266</v>
       </c>
-      <c r="AW89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX89" t="inlineStr">
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>10.1016/j.ces.2024.120716</t>
+        </is>
+      </c>
+      <c r="AX89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY89" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -14771,10 +15216,15 @@
       <c r="AV90" t="n">
         <v>3.093893946960023</v>
       </c>
-      <c r="AW90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX90" t="inlineStr">
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>10.1016/j.ces.2024.120716</t>
+        </is>
+      </c>
+      <c r="AX90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY90" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -14931,10 +15381,15 @@
       <c r="AV91" t="n">
         <v>1.568635433144139</v>
       </c>
-      <c r="AW91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX91" t="inlineStr">
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>10.4028/www.scientific.net/AMR.629.376</t>
+        </is>
+      </c>
+      <c r="AX91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY91" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -15091,10 +15546,15 @@
       <c r="AV92" t="n">
         <v>0.6821794308876921</v>
       </c>
-      <c r="AW92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX92" t="inlineStr">
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>10.1556/JFC-D-14-00035</t>
+        </is>
+      </c>
+      <c r="AX92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY92" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -15251,10 +15711,15 @@
       <c r="AV93" t="n">
         <v>0.950415014073698</v>
       </c>
-      <c r="AW93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX93" t="inlineStr">
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>10.1556/JFC-D-14-00035</t>
+        </is>
+      </c>
+      <c r="AX93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY93" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -15411,10 +15876,15 @@
       <c r="AV94" t="n">
         <v>0.8147204197217046</v>
       </c>
-      <c r="AW94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX94" t="inlineStr">
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>10.1556/JFC-D-14-00035</t>
+        </is>
+      </c>
+      <c r="AX94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY94" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -15571,10 +16041,15 @@
       <c r="AV95" t="n">
         <v>0.7069439946984121</v>
       </c>
-      <c r="AW95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX95" t="inlineStr">
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>10.1556/JFC-D-14-00035</t>
+        </is>
+      </c>
+      <c r="AX95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY95" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -15731,10 +16206,15 @@
       <c r="AV96" t="n">
         <v>0.5910992060277078</v>
       </c>
-      <c r="AW96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX96" t="inlineStr">
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>10.1039/C5RA05133A</t>
+        </is>
+      </c>
+      <c r="AX96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY96" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -15891,10 +16371,15 @@
       <c r="AV97" t="n">
         <v>0.8025740804504577</v>
       </c>
-      <c r="AW97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX97" t="inlineStr">
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>10.1039/C5RA05133A</t>
+        </is>
+      </c>
+      <c r="AX97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY97" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -16051,10 +16536,15 @@
       <c r="AV98" t="n">
         <v>0.9489437332901238</v>
       </c>
-      <c r="AW98" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX98" t="inlineStr">
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>10.1039/C5RA05133A</t>
+        </is>
+      </c>
+      <c r="AX98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY98" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -16211,10 +16701,15 @@
       <c r="AV99" t="n">
         <v>1.06557107267277</v>
       </c>
-      <c r="AW99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX99" t="inlineStr">
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>10.1039/C5RA05133A</t>
+        </is>
+      </c>
+      <c r="AX99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY99" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -16371,10 +16866,15 @@
       <c r="AV100" t="n">
         <v>1.07774902778903</v>
       </c>
-      <c r="AW100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX100" t="inlineStr">
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>10.1039/C5RA05133A</t>
+        </is>
+      </c>
+      <c r="AX100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY100" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -16531,10 +17031,15 @@
       <c r="AV101" t="n">
         <v>0.3129223271610692</v>
       </c>
-      <c r="AW101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX101" t="inlineStr">
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>10.1556/JFC-D-14-00035</t>
+        </is>
+      </c>
+      <c r="AX101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY101" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -16677,10 +17182,15 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AU102" t="inlineStr"/>
       <c r="AV102" t="inlineStr"/>
-      <c r="AW102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX102" t="inlineStr">
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
+      <c r="AX102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY102" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -16823,10 +17333,15 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AU103" t="inlineStr"/>
       <c r="AV103" t="inlineStr"/>
-      <c r="AW103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX103" t="inlineStr">
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
+      <c r="AX103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY103" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -16969,10 +17484,15 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AU104" t="inlineStr"/>
       <c r="AV104" t="inlineStr"/>
-      <c r="AW104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX104" t="inlineStr">
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
+      <c r="AX104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY104" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -17115,10 +17635,15 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AU105" t="inlineStr"/>
       <c r="AV105" t="inlineStr"/>
-      <c r="AW105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX105" t="inlineStr">
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
+      <c r="AX105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY105" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -17261,10 +17786,15 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AU106" t="inlineStr"/>
       <c r="AV106" t="inlineStr"/>
-      <c r="AW106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX106" t="inlineStr">
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
+      <c r="AX106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY106" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -17407,10 +17937,15 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AU107" t="inlineStr"/>
       <c r="AV107" t="inlineStr"/>
-      <c r="AW107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX107" t="inlineStr">
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
+      <c r="AX107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY107" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -17553,10 +18088,15 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AU108" t="inlineStr"/>
       <c r="AV108" t="inlineStr"/>
-      <c r="AW108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX108" t="inlineStr">
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
+      <c r="AX108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY108" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -17699,10 +18239,15 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AU109" t="inlineStr"/>
       <c r="AV109" t="inlineStr"/>
-      <c r="AW109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX109" t="inlineStr">
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
+      <c r="AX109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY109" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -17845,10 +18390,15 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AU110" t="inlineStr"/>
       <c r="AV110" t="inlineStr"/>
-      <c r="AW110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX110" t="inlineStr">
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
+      <c r="AX110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY110" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -17991,10 +18541,15 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AU111" t="inlineStr"/>
       <c r="AV111" t="inlineStr"/>
-      <c r="AW111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX111" t="inlineStr">
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
+      <c r="AX111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY111" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -18137,10 +18692,15 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AU112" t="inlineStr"/>
       <c r="AV112" t="inlineStr"/>
-      <c r="AW112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX112" t="inlineStr">
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
+      <c r="AX112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY112" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -18295,10 +18855,15 @@
       <c r="AV113" t="n">
         <v>0.7978073570911253</v>
       </c>
-      <c r="AW113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX113" t="inlineStr">
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>10.1039/D2CY00447J</t>
+        </is>
+      </c>
+      <c r="AX113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY113" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -18445,10 +19010,15 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AU114" t="inlineStr"/>
       <c r="AV114" t="inlineStr"/>
-      <c r="AW114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX114" t="inlineStr">
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>10.1039/c7cc04574c</t>
+        </is>
+      </c>
+      <c r="AX114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY114" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -18603,10 +19173,15 @@
       <c r="AV115" t="n">
         <v>0.1913143370876304</v>
       </c>
-      <c r="AW115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX115" t="inlineStr">
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>10.1039/D2CY00447J</t>
+        </is>
+      </c>
+      <c r="AX115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY115" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -18753,10 +19328,15 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AU116" t="inlineStr"/>
       <c r="AV116" t="inlineStr"/>
-      <c r="AW116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX116" t="inlineStr">
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>10.1039/c7cc04574c</t>
+        </is>
+      </c>
+      <c r="AX116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY116" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -18903,10 +19483,15 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AU117" t="inlineStr"/>
       <c r="AV117" t="inlineStr"/>
-      <c r="AW117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX117" t="inlineStr">
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>10.1039/c7cc04574c</t>
+        </is>
+      </c>
+      <c r="AX117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY117" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -19061,10 +19646,15 @@
       <c r="AV118" t="n">
         <v>0.5785930125115488</v>
       </c>
-      <c r="AW118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX118" t="inlineStr">
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>10.1039/D2CY00447J</t>
+        </is>
+      </c>
+      <c r="AX118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY118" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -19211,10 +19801,15 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AU119" t="inlineStr"/>
       <c r="AV119" t="inlineStr"/>
-      <c r="AW119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX119" t="inlineStr">
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>10.1039/c7cc04574c</t>
+        </is>
+      </c>
+      <c r="AX119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY119" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -19361,10 +19956,15 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AU120" t="inlineStr"/>
       <c r="AV120" t="inlineStr"/>
-      <c r="AW120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX120" t="inlineStr">
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>10.1039/c7cc04574c</t>
+        </is>
+      </c>
+      <c r="AX120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY120" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -19511,10 +20111,15 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AU121" t="inlineStr"/>
       <c r="AV121" t="inlineStr"/>
-      <c r="AW121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX121" t="inlineStr">
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>10.1039/c7cc04574c</t>
+        </is>
+      </c>
+      <c r="AX121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY121" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -19659,10 +20264,15 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AU122" t="inlineStr"/>
       <c r="AV122" t="inlineStr"/>
-      <c r="AW122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX122" t="inlineStr">
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>10.1016/S1872‐2067(18)63069‐4</t>
+        </is>
+      </c>
+      <c r="AX122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY122" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -19807,10 +20417,15 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AU123" t="inlineStr"/>
       <c r="AV123" t="inlineStr"/>
-      <c r="AW123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX123" t="inlineStr">
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>10.1016/S1872‐2067(18)63069‐4</t>
+        </is>
+      </c>
+      <c r="AX123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY123" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -19955,10 +20570,15 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AU124" t="inlineStr"/>
       <c r="AV124" t="inlineStr"/>
-      <c r="AW124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX124" t="inlineStr">
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>10.1016/S1872-2067(18)63145-6</t>
+        </is>
+      </c>
+      <c r="AX124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY124" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -20103,10 +20723,15 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AU125" t="inlineStr"/>
       <c r="AV125" t="inlineStr"/>
-      <c r="AW125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX125" t="inlineStr">
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>10.1016/S1872-2067(18)63145-6</t>
+        </is>
+      </c>
+      <c r="AX125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY125" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -20251,10 +20876,15 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AU126" t="inlineStr"/>
       <c r="AV126" t="inlineStr"/>
-      <c r="AW126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX126" t="inlineStr">
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>10.1016/S1872-2067(18)63145-6</t>
+        </is>
+      </c>
+      <c r="AX126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY126" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -20407,10 +21037,15 @@
       <c r="AV127" t="n">
         <v>1.06119671353295</v>
       </c>
-      <c r="AW127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX127" t="inlineStr">
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>10.1039/D2CY00447J</t>
+        </is>
+      </c>
+      <c r="AX127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY127" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -20563,10 +21198,15 @@
       <c r="AV128" t="n">
         <v>0.656978747846064</v>
       </c>
-      <c r="AW128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX128" t="inlineStr">
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>10.1039/D2CY00447J</t>
+        </is>
+      </c>
+      <c r="AX128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY128" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -20719,10 +21359,15 @@
       <c r="AV129" t="n">
         <v>1.498628973853105</v>
       </c>
-      <c r="AW129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX129" t="inlineStr">
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>10.1039/D2CY00447J</t>
+        </is>
+      </c>
+      <c r="AX129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY129" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -20875,10 +21520,15 @@
       <c r="AV130" t="n">
         <v>0.9854681217690963</v>
       </c>
-      <c r="AW130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX130" t="inlineStr">
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>10.1039/D2CY00447J</t>
+        </is>
+      </c>
+      <c r="AX130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY130" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -21025,10 +21675,15 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AU131" t="inlineStr"/>
       <c r="AV131" t="inlineStr"/>
-      <c r="AW131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX131" t="inlineStr">
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>10.1039/c7cc04574c</t>
+        </is>
+      </c>
+      <c r="AX131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY131" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -21177,10 +21832,15 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AU132" t="inlineStr"/>
       <c r="AV132" t="inlineStr"/>
-      <c r="AW132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX132" t="inlineStr">
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b02841</t>
+        </is>
+      </c>
+      <c r="AX132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY132" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -21329,10 +21989,15 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AU133" t="inlineStr"/>
       <c r="AV133" t="inlineStr"/>
-      <c r="AW133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX133" t="inlineStr">
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b02841</t>
+        </is>
+      </c>
+      <c r="AX133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY133" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -21475,10 +22140,15 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AU134" t="inlineStr"/>
       <c r="AV134" t="inlineStr"/>
-      <c r="AW134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX134" t="inlineStr">
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
+      <c r="AX134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY134" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -21631,10 +22301,15 @@
       <c r="AV135" t="n">
         <v>1.586163584424854</v>
       </c>
-      <c r="AW135" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX135" t="inlineStr">
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>10.1039/D2RA06960A</t>
+        </is>
+      </c>
+      <c r="AX135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY135" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -21787,10 +22462,15 @@
       <c r="AV136" t="n">
         <v>4.07557385098487</v>
       </c>
-      <c r="AW136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX136" t="inlineStr">
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>10.1002/jctb.6360</t>
+        </is>
+      </c>
+      <c r="AX136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY136" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -21939,10 +22619,15 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AU137" t="inlineStr"/>
       <c r="AV137" t="inlineStr"/>
-      <c r="AW137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX137" t="inlineStr">
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b02841</t>
+        </is>
+      </c>
+      <c r="AX137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY137" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -22095,10 +22780,15 @@
       <c r="AV138" t="n">
         <v>0.5065107991360693</v>
       </c>
-      <c r="AW138" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX138" t="inlineStr">
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
+      <c r="AX138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY138" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -22251,10 +22941,15 @@
       <c r="AV139" t="n">
         <v>1.113617612184385</v>
       </c>
-      <c r="AW139" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX139" t="inlineStr">
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>10.1039/D2RA06960A</t>
+        </is>
+      </c>
+      <c r="AX139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY139" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -22407,10 +23102,15 @@
       <c r="AV140" t="n">
         <v>0.1455692410367171</v>
       </c>
-      <c r="AW140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX140" t="inlineStr">
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
+      <c r="AX140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY140" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -22563,10 +23263,15 @@
       <c r="AV141" t="n">
         <v>0.2176466184881211</v>
       </c>
-      <c r="AW141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX141" t="inlineStr">
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
+      <c r="AX141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY141" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -22715,10 +23420,15 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AU142" t="inlineStr"/>
       <c r="AV142" t="inlineStr"/>
-      <c r="AW142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX142" t="inlineStr">
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b02841</t>
+        </is>
+      </c>
+      <c r="AX142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY142" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -22871,10 +23581,15 @@
       <c r="AV143" t="n">
         <v>0.05560799136069117</v>
       </c>
-      <c r="AW143" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX143" t="inlineStr">
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
+      <c r="AX143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY143" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -23027,10 +23742,15 @@
       <c r="AV144" t="n">
         <v>3.739272570194384</v>
       </c>
-      <c r="AW144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX144" t="inlineStr">
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiec.2014.11.014</t>
+        </is>
+      </c>
+      <c r="AX144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY144" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -23189,10 +23909,15 @@
       <c r="AV145" t="n">
         <v>0</v>
       </c>
-      <c r="AW145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX145" t="inlineStr">
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>10.1007/s11144-018-1419-8</t>
+        </is>
+      </c>
+      <c r="AX145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY145" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -23351,10 +24076,15 @@
       <c r="AV146" t="n">
         <v>3.197042635550025</v>
       </c>
-      <c r="AW146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX146" t="inlineStr">
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>10.1007/s11144-018-1419-8</t>
+        </is>
+      </c>
+      <c r="AX146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY146" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -23497,10 +24227,15 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AU147" t="inlineStr"/>
       <c r="AV147" t="inlineStr"/>
-      <c r="AW147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX147" t="inlineStr">
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
+      <c r="AX147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY147" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -23643,10 +24378,15 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AU148" t="inlineStr"/>
       <c r="AV148" t="inlineStr"/>
-      <c r="AW148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX148" t="inlineStr">
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
+      <c r="AX148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY148" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -23789,10 +24529,15 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AU149" t="inlineStr"/>
       <c r="AV149" t="inlineStr"/>
-      <c r="AW149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX149" t="inlineStr">
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
+      <c r="AX149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY149" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -23935,10 +24680,15 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AU150" t="inlineStr"/>
       <c r="AV150" t="inlineStr"/>
-      <c r="AW150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX150" t="inlineStr">
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
+      <c r="AX150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY150" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -24081,10 +24831,15 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AU151" t="inlineStr"/>
       <c r="AV151" t="inlineStr"/>
-      <c r="AW151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX151" t="inlineStr">
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
+      <c r="AX151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY151" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -24227,10 +24982,15 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AU152" t="inlineStr"/>
       <c r="AV152" t="inlineStr"/>
-      <c r="AW152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX152" t="inlineStr">
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
+      <c r="AX152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY152" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -24373,10 +25133,15 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AU153" t="inlineStr"/>
       <c r="AV153" t="inlineStr"/>
-      <c r="AW153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX153" t="inlineStr">
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
+      <c r="AX153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY153" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -24519,10 +25284,15 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AU154" t="inlineStr"/>
       <c r="AV154" t="inlineStr"/>
-      <c r="AW154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX154" t="inlineStr">
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
+      <c r="AX154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY154" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -24665,10 +25435,15 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AU155" t="inlineStr"/>
       <c r="AV155" t="inlineStr"/>
-      <c r="AW155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX155" t="inlineStr">
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>10.1021/i360017a011</t>
+        </is>
+      </c>
+      <c r="AX155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY155" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -24817,10 +25592,15 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AU156" t="inlineStr"/>
       <c r="AV156" t="inlineStr"/>
-      <c r="AW156" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX156" t="inlineStr">
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2609-8</t>
+        </is>
+      </c>
+      <c r="AX156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY156" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -24969,10 +25749,15 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AU157" t="inlineStr"/>
       <c r="AV157" t="inlineStr"/>
-      <c r="AW157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX157" t="inlineStr">
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2609-8</t>
+        </is>
+      </c>
+      <c r="AX157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY157" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -25121,10 +25906,15 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AU158" t="inlineStr"/>
       <c r="AV158" t="inlineStr"/>
-      <c r="AW158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX158" t="inlineStr">
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2609-8</t>
+        </is>
+      </c>
+      <c r="AX158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY158" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -25273,10 +26063,15 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AU159" t="inlineStr"/>
       <c r="AV159" t="inlineStr"/>
-      <c r="AW159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX159" t="inlineStr">
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b02841</t>
+        </is>
+      </c>
+      <c r="AX159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY159" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -25429,10 +26224,15 @@
       <c r="AV160" t="n">
         <v>0.3341511879049677</v>
       </c>
-      <c r="AW160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX160" t="inlineStr">
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
+      <c r="AX160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY160" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -25591,10 +26391,15 @@
       <c r="AV161" t="n">
         <v>0.006491810919825448</v>
       </c>
-      <c r="AW161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX161" t="inlineStr">
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.1c04460</t>
+        </is>
+      </c>
+      <c r="AX161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY161" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -25747,10 +26552,15 @@
       <c r="AV162" t="n">
         <v>0.1319975760235733</v>
       </c>
-      <c r="AW162" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX162" t="inlineStr">
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>10.1021/acssuschemeng.0c05916</t>
+        </is>
+      </c>
+      <c r="AX162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY162" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -25909,10 +26719,15 @@
       <c r="AV163" t="n">
         <v>4.665167584648525</v>
       </c>
-      <c r="AW163" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX163" t="inlineStr">
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2535-9</t>
+        </is>
+      </c>
+      <c r="AX163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY163" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -26071,10 +26886,15 @@
       <c r="AV164" t="n">
         <v>9.182349604318869</v>
       </c>
-      <c r="AW164" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX164" t="inlineStr">
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2535-9</t>
+        </is>
+      </c>
+      <c r="AX164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY164" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -26227,10 +27047,15 @@
       <c r="AV165" t="n">
         <v>0.2023023758099353</v>
       </c>
-      <c r="AW165" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX165" t="inlineStr">
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
+      <c r="AX165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY165" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -26389,10 +27214,15 @@
       <c r="AV166" t="n">
         <v>14.90164668850127</v>
       </c>
-      <c r="AW166" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX166" t="inlineStr">
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2535-9</t>
+        </is>
+      </c>
+      <c r="AX166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY166" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -26551,10 +27381,15 @@
       <c r="AV167" t="n">
         <v>20.23223498611898</v>
       </c>
-      <c r="AW167" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX167" t="inlineStr">
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>10.1007/s10562-018-2535-9</t>
+        </is>
+      </c>
+      <c r="AX167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY167" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -26699,10 +27534,15 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AU168" t="inlineStr"/>
       <c r="AV168" t="inlineStr"/>
-      <c r="AW168" t="n">
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>10.1109/NAP.2017.8190167</t>
+        </is>
+      </c>
+      <c r="AX168" t="n">
         <v>2</v>
       </c>
-      <c r="AX168" t="inlineStr">
+      <c r="AY168" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -26847,10 +27687,15 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AU169" t="inlineStr"/>
       <c r="AV169" t="inlineStr"/>
-      <c r="AW169" t="n">
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>10.1007/s11144-018-1443-8</t>
+        </is>
+      </c>
+      <c r="AX169" t="n">
         <v>2</v>
       </c>
-      <c r="AX169" t="inlineStr">
+      <c r="AY169" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -26995,10 +27840,15 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AU170" t="inlineStr"/>
       <c r="AV170" t="inlineStr"/>
-      <c r="AW170" t="n">
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>10.1007/s11144-018-1443-8</t>
+        </is>
+      </c>
+      <c r="AX170" t="n">
         <v>2</v>
       </c>
-      <c r="AX170" t="inlineStr">
+      <c r="AY170" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -27143,10 +27993,15 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AU171" t="inlineStr"/>
       <c r="AV171" t="inlineStr"/>
-      <c r="AW171" t="n">
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>10.1007/s11144-018-1443-8</t>
+        </is>
+      </c>
+      <c r="AX171" t="n">
         <v>2</v>
       </c>
-      <c r="AX171" t="inlineStr">
+      <c r="AY171" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -27291,10 +28146,15 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AU172" t="inlineStr"/>
       <c r="AV172" t="inlineStr"/>
-      <c r="AW172" t="n">
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>10.1007/s11144-018-1443-8</t>
+        </is>
+      </c>
+      <c r="AX172" t="n">
         <v>2</v>
       </c>
-      <c r="AX172" t="inlineStr">
+      <c r="AY172" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -27447,10 +28307,15 @@
       <c r="AV173" t="n">
         <v>0.8264491835392516</v>
       </c>
-      <c r="AW173" t="n">
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2022.137324</t>
+        </is>
+      </c>
+      <c r="AX173" t="n">
         <v>2</v>
       </c>
-      <c r="AX173" t="inlineStr">
+      <c r="AY173" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -27603,10 +28468,15 @@
       <c r="AV174" t="n">
         <v>2.051033978527193</v>
       </c>
-      <c r="AW174" t="n">
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2022.137324</t>
+        </is>
+      </c>
+      <c r="AX174" t="n">
         <v>2</v>
       </c>
-      <c r="AX174" t="inlineStr">
+      <c r="AY174" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -27759,10 +28629,15 @@
       <c r="AV175" t="n">
         <v>2.283383057791335</v>
       </c>
-      <c r="AW175" t="n">
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2022.137324</t>
+        </is>
+      </c>
+      <c r="AX175" t="n">
         <v>2</v>
       </c>
-      <c r="AX175" t="inlineStr">
+      <c r="AY175" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -27917,10 +28792,15 @@
       <c r="AV176" t="n">
         <v>1.294475002881371</v>
       </c>
-      <c r="AW176" t="n">
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2023.128414</t>
+        </is>
+      </c>
+      <c r="AX176" t="n">
         <v>2</v>
       </c>
-      <c r="AX176" t="inlineStr">
+      <c r="AY176" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -28075,10 +28955,15 @@
       <c r="AV177" t="n">
         <v>1.766123877216917</v>
       </c>
-      <c r="AW177" t="n">
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2023.128414</t>
+        </is>
+      </c>
+      <c r="AX177" t="n">
         <v>2</v>
       </c>
-      <c r="AX177" t="inlineStr">
+      <c r="AY177" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -28233,10 +29118,15 @@
       <c r="AV178" t="n">
         <v>2.891139794209217</v>
       </c>
-      <c r="AW178" t="n">
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2023.128414</t>
+        </is>
+      </c>
+      <c r="AX178" t="n">
         <v>2</v>
       </c>
-      <c r="AX178" t="inlineStr">
+      <c r="AY178" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -28391,10 +29281,15 @@
       <c r="AV179" t="n">
         <v>1.630842938154373</v>
       </c>
-      <c r="AW179" t="n">
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>10.1039/D2CC06618A</t>
+        </is>
+      </c>
+      <c r="AX179" t="n">
         <v>2</v>
       </c>
-      <c r="AX179" t="inlineStr">
+      <c r="AY179" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -28549,10 +29444,15 @@
       <c r="AV180" t="n">
         <v>2.629351562383224</v>
       </c>
-      <c r="AW180" t="n">
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>10.1039/D2CC06618A</t>
+        </is>
+      </c>
+      <c r="AX180" t="n">
         <v>2</v>
       </c>
-      <c r="AX180" t="inlineStr">
+      <c r="AY180" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -28707,10 +29607,15 @@
       <c r="AV181" t="n">
         <v>7.338151450099357</v>
       </c>
-      <c r="AW181" t="n">
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>10.1039/D2CC06618A</t>
+        </is>
+      </c>
+      <c r="AX181" t="n">
         <v>2</v>
       </c>
-      <c r="AX181" t="inlineStr">
+      <c r="AY181" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -28863,10 +29768,15 @@
       <c r="AV182" t="n">
         <v>0.8909859611231106</v>
       </c>
-      <c r="AW182" t="n">
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
+      <c r="AX182" t="n">
         <v>2</v>
       </c>
-      <c r="AX182" t="inlineStr">
+      <c r="AY182" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -29019,10 +29929,15 @@
       <c r="AV183" t="n">
         <v>0.972259179265659</v>
       </c>
-      <c r="AW183" t="n">
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
+      <c r="AX183" t="n">
         <v>2</v>
       </c>
-      <c r="AX183" t="inlineStr">
+      <c r="AY183" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -29167,10 +30082,15 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AU184" t="inlineStr"/>
       <c r="AV184" t="inlineStr"/>
-      <c r="AW184" t="n">
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>10.1007/s11237-020-09658-y</t>
+        </is>
+      </c>
+      <c r="AX184" t="n">
         <v>2</v>
       </c>
-      <c r="AX184" t="inlineStr">
+      <c r="AY184" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -29321,10 +30241,15 @@
       <c r="AV185" t="n">
         <v>2.486910633042796</v>
       </c>
-      <c r="AW185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX185" t="inlineStr">
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiec.2016.06.018</t>
+        </is>
+      </c>
+      <c r="AX185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY185" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -29475,10 +30400,15 @@
       <c r="AV186" t="n">
         <v>4.218909578452532</v>
       </c>
-      <c r="AW186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX186" t="inlineStr">
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiec.2016.06.018</t>
+        </is>
+      </c>
+      <c r="AX186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY186" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -29631,10 +30561,15 @@
       <c r="AV187" t="n">
         <v>1.166689041354884</v>
       </c>
-      <c r="AW187" t="n">
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>10.1039/D3NJ00221G</t>
+        </is>
+      </c>
+      <c r="AX187" t="n">
         <v>2</v>
       </c>
-      <c r="AX187" t="inlineStr">
+      <c r="AY187" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -29787,10 +30722,15 @@
       <c r="AV188" t="n">
         <v>0.8882615471525995</v>
       </c>
-      <c r="AW188" t="n">
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>10.1038/s41598-019-53180-8</t>
+        </is>
+      </c>
+      <c r="AX188" t="n">
         <v>2</v>
       </c>
-      <c r="AX188" t="inlineStr">
+      <c r="AY188" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -29943,10 +30883,15 @@
       <c r="AV189" t="n">
         <v>0.8248099352051836</v>
       </c>
-      <c r="AW189" t="n">
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
+      <c r="AX189" t="n">
         <v>2</v>
       </c>
-      <c r="AX189" t="inlineStr">
+      <c r="AY189" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -30097,10 +31042,15 @@
       <c r="AV190" t="n">
         <v>0.50102</v>
       </c>
-      <c r="AW190" t="n">
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>10.1016/0021-9517(87)90285-5</t>
+        </is>
+      </c>
+      <c r="AX190" t="n">
         <v>2</v>
       </c>
-      <c r="AX190" t="inlineStr">
+      <c r="AY190" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -30251,10 +31201,15 @@
       <c r="AV191" t="n">
         <v>0.466193</v>
       </c>
-      <c r="AW191" t="n">
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>10.1016/0021-9517(87)90285-5</t>
+        </is>
+      </c>
+      <c r="AX191" t="n">
         <v>2</v>
       </c>
-      <c r="AX191" t="inlineStr">
+      <c r="AY191" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -30405,10 +31360,15 @@
       <c r="AV192" t="n">
         <v>0.1794</v>
       </c>
-      <c r="AW192" t="n">
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>10.1016/0021-9517(87)90285-5</t>
+        </is>
+      </c>
+      <c r="AX192" t="n">
         <v>2</v>
       </c>
-      <c r="AX192" t="inlineStr">
+      <c r="AY192" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -30559,10 +31519,15 @@
       <c r="AV193" t="n">
         <v>0.833</v>
       </c>
-      <c r="AW193" t="n">
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>10.1016/0021-9517(87)90285-5</t>
+        </is>
+      </c>
+      <c r="AX193" t="n">
         <v>2</v>
       </c>
-      <c r="AX193" t="inlineStr">
+      <c r="AY193" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -30713,10 +31678,15 @@
       <c r="AV194" t="n">
         <v>0.7726500000000001</v>
       </c>
-      <c r="AW194" t="n">
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>10.1016/0021-9517(87)90285-5</t>
+        </is>
+      </c>
+      <c r="AX194" t="n">
         <v>2</v>
       </c>
-      <c r="AX194" t="inlineStr">
+      <c r="AY194" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -30867,10 +31837,15 @@
       <c r="AV195" t="n">
         <v>0.2715</v>
       </c>
-      <c r="AW195" t="n">
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>10.1016/0021-9517(87)90285-5</t>
+        </is>
+      </c>
+      <c r="AX195" t="n">
         <v>2</v>
       </c>
-      <c r="AX195" t="inlineStr">
+      <c r="AY195" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -31021,10 +31996,15 @@
       <c r="AV196" t="n">
         <v>0.6375</v>
       </c>
-      <c r="AW196" t="n">
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>10.1016/0021-9517(87)90285-5</t>
+        </is>
+      </c>
+      <c r="AX196" t="n">
         <v>2</v>
       </c>
-      <c r="AX196" t="inlineStr">
+      <c r="AY196" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -31175,10 +32155,15 @@
       <c r="AV197" t="n">
         <v>0.6034999999999999</v>
       </c>
-      <c r="AW197" t="n">
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>10.1016/0021-9517(87)90285-5</t>
+        </is>
+      </c>
+      <c r="AX197" t="n">
         <v>2</v>
       </c>
-      <c r="AX197" t="inlineStr">
+      <c r="AY197" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -31329,10 +32314,15 @@
       <c r="AV198" t="n">
         <v>0.7055</v>
       </c>
-      <c r="AW198" t="n">
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>10.1016/0021-9517(87)90285-5</t>
+        </is>
+      </c>
+      <c r="AX198" t="n">
         <v>2</v>
       </c>
-      <c r="AX198" t="inlineStr">
+      <c r="AY198" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -31483,10 +32473,15 @@
       <c r="AV199" t="n">
         <v>0.374</v>
       </c>
-      <c r="AW199" t="n">
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>10.1016/0021-9517(87)90285-5</t>
+        </is>
+      </c>
+      <c r="AX199" t="n">
         <v>2</v>
       </c>
-      <c r="AX199" t="inlineStr">
+      <c r="AY199" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -31637,10 +32632,15 @@
       <c r="AV200" t="n">
         <v>5.998416666666667</v>
       </c>
-      <c r="AW200" t="n">
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>10.1016/S0166-9834(00)80265-1</t>
+        </is>
+      </c>
+      <c r="AX200" t="n">
         <v>2</v>
       </c>
-      <c r="AX200" t="inlineStr">
+      <c r="AY200" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -31791,10 +32791,15 @@
       <c r="AV201" t="n">
         <v>5.839166666666666</v>
       </c>
-      <c r="AW201" t="n">
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>10.1016/S0166-9834(00)80265-1</t>
+        </is>
+      </c>
+      <c r="AX201" t="n">
         <v>2</v>
       </c>
-      <c r="AX201" t="inlineStr">
+      <c r="AY201" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -31945,10 +32950,15 @@
       <c r="AV202" t="n">
         <v>5.159000000000001</v>
       </c>
-      <c r="AW202" t="n">
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>10.1016/S0166-9834(00)80265-1</t>
+        </is>
+      </c>
+      <c r="AX202" t="n">
         <v>2</v>
       </c>
-      <c r="AX202" t="inlineStr">
+      <c r="AY202" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -32099,10 +33109,15 @@
       <c r="AV203" t="n">
         <v>9.084250000000001</v>
       </c>
-      <c r="AW203" t="n">
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>10.1016/S0166-9834(00)80265-1</t>
+        </is>
+      </c>
+      <c r="AX203" t="n">
         <v>2</v>
       </c>
-      <c r="AX203" t="inlineStr">
+      <c r="AY203" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -32253,10 +33268,15 @@
       <c r="AV204" t="n">
         <v>6.850200000000001</v>
       </c>
-      <c r="AW204" t="n">
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>10.1016/S0166-9834(00)80265-1</t>
+        </is>
+      </c>
+      <c r="AX204" t="n">
         <v>2</v>
       </c>
-      <c r="AX204" t="inlineStr">
+      <c r="AY204" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -32407,10 +33427,15 @@
       <c r="AV205" t="n">
         <v>4.841136363636362</v>
       </c>
-      <c r="AW205" t="n">
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>10.1016/S0166-9834(00)82351-9</t>
+        </is>
+      </c>
+      <c r="AX205" t="n">
         <v>2</v>
       </c>
-      <c r="AX205" t="inlineStr">
+      <c r="AY205" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -32561,10 +33586,15 @@
       <c r="AV206" t="n">
         <v>2.38175</v>
       </c>
-      <c r="AW206" t="n">
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>10.1016/S0166-9834(00)82351-9</t>
+        </is>
+      </c>
+      <c r="AX206" t="n">
         <v>2</v>
       </c>
-      <c r="AX206" t="inlineStr">
+      <c r="AY206" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -32715,10 +33745,15 @@
       <c r="AV207" t="n">
         <v>0.7669374999999999</v>
       </c>
-      <c r="AW207" t="n">
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>10.1016/S0166-9834(00)82351-9</t>
+        </is>
+      </c>
+      <c r="AX207" t="n">
         <v>2</v>
       </c>
-      <c r="AX207" t="inlineStr">
+      <c r="AY207" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -32869,10 +33904,15 @@
       <c r="AV208" t="n">
         <v>6.244318181818182</v>
       </c>
-      <c r="AW208" t="n">
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>10.1016/S0166-9834(00)82351-9</t>
+        </is>
+      </c>
+      <c r="AX208" t="n">
         <v>2</v>
       </c>
-      <c r="AX208" t="inlineStr">
+      <c r="AY208" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -33023,10 +34063,15 @@
       <c r="AV209" t="n">
         <v>3.21895</v>
       </c>
-      <c r="AW209" t="n">
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>10.1016/S0166-9834(00)82351-9</t>
+        </is>
+      </c>
+      <c r="AX209" t="n">
         <v>2</v>
       </c>
-      <c r="AX209" t="inlineStr">
+      <c r="AY209" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -33173,10 +34218,15 @@
         <v>0.4</v>
       </c>
       <c r="AV210" t="inlineStr"/>
-      <c r="AW210" t="n">
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>10.1016/S0167-2991(08)61662-6</t>
+        </is>
+      </c>
+      <c r="AX210" t="n">
         <v>2</v>
       </c>
-      <c r="AX210" t="inlineStr">
+      <c r="AY210" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -33323,10 +34373,15 @@
         <v>0.4</v>
       </c>
       <c r="AV211" t="inlineStr"/>
-      <c r="AW211" t="n">
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>10.1016/S0167-2991(08)61662-6</t>
+        </is>
+      </c>
+      <c r="AX211" t="n">
         <v>2</v>
       </c>
-      <c r="AX211" t="inlineStr">
+      <c r="AY211" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -33473,10 +34528,15 @@
         <v>0.4</v>
       </c>
       <c r="AV212" t="inlineStr"/>
-      <c r="AW212" t="n">
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>10.1016/S0167-2991(08)61662-6</t>
+        </is>
+      </c>
+      <c r="AX212" t="n">
         <v>2</v>
       </c>
-      <c r="AX212" t="inlineStr">
+      <c r="AY212" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -33625,10 +34685,15 @@
         <v>0.4</v>
       </c>
       <c r="AV213" t="inlineStr"/>
-      <c r="AW213" t="n">
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>10.1016/S0167-2991(08)61662-6</t>
+        </is>
+      </c>
+      <c r="AX213" t="n">
         <v>2</v>
       </c>
-      <c r="AX213" t="inlineStr">
+      <c r="AY213" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -33783,10 +34848,15 @@
       <c r="AV214" t="n">
         <v>1.19</v>
       </c>
-      <c r="AW214" t="n">
+      <c r="AW214" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcat.2014.04.005</t>
+        </is>
+      </c>
+      <c r="AX214" t="n">
         <v>2</v>
       </c>
-      <c r="AX214" t="inlineStr">
+      <c r="AY214" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -33939,10 +35009,15 @@
       <c r="AV215" t="n">
         <v>1.715683220312576</v>
       </c>
-      <c r="AW215" t="n">
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcat.2019.04.032</t>
+        </is>
+      </c>
+      <c r="AX215" t="n">
         <v>2</v>
       </c>
-      <c r="AX215" t="inlineStr">
+      <c r="AY215" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -34095,10 +35170,15 @@
       <c r="AV216" t="n">
         <v>4.258643622866135</v>
       </c>
-      <c r="AW216" t="n">
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcat.2019.04.032</t>
+        </is>
+      </c>
+      <c r="AX216" t="n">
         <v>2</v>
       </c>
-      <c r="AX216" t="inlineStr">
+      <c r="AY216" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -34251,10 +35331,15 @@
       <c r="AV217" t="n">
         <v>0.7641106978826797</v>
       </c>
-      <c r="AW217" t="n">
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcat.2019.04.032</t>
+        </is>
+      </c>
+      <c r="AX217" t="n">
         <v>2</v>
       </c>
-      <c r="AX217" t="inlineStr">
+      <c r="AY217" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -34407,10 +35492,15 @@
       <c r="AV218" t="n">
         <v>1.114582804644869</v>
       </c>
-      <c r="AW218" t="n">
+      <c r="AW218" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcat.2019.04.032</t>
+        </is>
+      </c>
+      <c r="AX218" t="n">
         <v>2</v>
       </c>
-      <c r="AX218" t="inlineStr">
+      <c r="AY218" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -34563,10 +35653,15 @@
       <c r="AV219" t="n">
         <v>1.328533800052019</v>
       </c>
-      <c r="AW219" t="n">
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcat.2019.04.032</t>
+        </is>
+      </c>
+      <c r="AX219" t="n">
         <v>2</v>
       </c>
-      <c r="AX219" t="inlineStr">
+      <c r="AY219" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -34719,10 +35814,15 @@
       <c r="AV220" t="n">
         <v>1.318345657413583</v>
       </c>
-      <c r="AW220" t="n">
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcat.2019.04.032</t>
+        </is>
+      </c>
+      <c r="AX220" t="n">
         <v>2</v>
       </c>
-      <c r="AX220" t="inlineStr">
+      <c r="AY220" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -34875,10 +35975,15 @@
       <c r="AV221" t="n">
         <v>1.428377597908689</v>
       </c>
-      <c r="AW221" t="n">
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcat.2019.04.032</t>
+        </is>
+      </c>
+      <c r="AX221" t="n">
         <v>2</v>
       </c>
-      <c r="AX221" t="inlineStr">
+      <c r="AY221" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -35031,10 +36136,15 @@
       <c r="AV222" t="n">
         <v>1.110507547589495</v>
       </c>
-      <c r="AW222" t="n">
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcat.2019.04.032</t>
+        </is>
+      </c>
+      <c r="AX222" t="n">
         <v>2</v>
       </c>
-      <c r="AX222" t="inlineStr">
+      <c r="AY222" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -35187,10 +36297,15 @@
       <c r="AV223" t="n">
         <v>2.435961924077114</v>
       </c>
-      <c r="AW223" t="n">
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t>10.1039/C9CC08700A</t>
+        </is>
+      </c>
+      <c r="AX223" t="n">
         <v>2</v>
       </c>
-      <c r="AX223" t="inlineStr">
+      <c r="AY223" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -35343,10 +36458,15 @@
       <c r="AV224" t="n">
         <v>3.247949232102819</v>
       </c>
-      <c r="AW224" t="n">
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>10.1039/C9CC08700A</t>
+        </is>
+      </c>
+      <c r="AX224" t="n">
         <v>2</v>
       </c>
-      <c r="AX224" t="inlineStr">
+      <c r="AY224" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -35499,10 +36619,15 @@
       <c r="AV225" t="n">
         <v>3.846883326914776</v>
       </c>
-      <c r="AW225" t="n">
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>10.1039/D2RA06960A</t>
+        </is>
+      </c>
+      <c r="AX225" t="n">
         <v>2</v>
       </c>
-      <c r="AX225" t="inlineStr">
+      <c r="AY225" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -35655,10 +36780,15 @@
       <c r="AV226" t="n">
         <v>3.546521561418445</v>
       </c>
-      <c r="AW226" t="n">
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t>10.1039/D2RA06960A</t>
+        </is>
+      </c>
+      <c r="AX226" t="n">
         <v>2</v>
       </c>
-      <c r="AX226" t="inlineStr">
+      <c r="AY226" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -35811,10 +36941,15 @@
       <c r="AV227" t="n">
         <v>2.792856697240634</v>
       </c>
-      <c r="AW227" t="n">
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>10.1039/D2RA06960A</t>
+        </is>
+      </c>
+      <c r="AX227" t="n">
         <v>2</v>
       </c>
-      <c r="AX227" t="inlineStr">
+      <c r="AY227" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -35967,10 +37102,15 @@
       <c r="AV228" t="n">
         <v>2.242416016515497</v>
       </c>
-      <c r="AW228" t="n">
+      <c r="AW228" t="inlineStr">
+        <is>
+          <t>10.1039/D2RA06960A</t>
+        </is>
+      </c>
+      <c r="AX228" t="n">
         <v>2</v>
       </c>
-      <c r="AX228" t="inlineStr">
+      <c r="AY228" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -36123,10 +37263,15 @@
       <c r="AV229" t="n">
         <v>1.248842148334175</v>
       </c>
-      <c r="AW229" t="n">
+      <c r="AW229" t="inlineStr">
+        <is>
+          <t>10.1039/D3NJ00221G</t>
+        </is>
+      </c>
+      <c r="AX229" t="n">
         <v>2</v>
       </c>
-      <c r="AX229" t="inlineStr">
+      <c r="AY229" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -36279,10 +37424,15 @@
       <c r="AV230" t="n">
         <v>1.256074812674627</v>
       </c>
-      <c r="AW230" t="n">
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t>10.1039/D3NJ00221G</t>
+        </is>
+      </c>
+      <c r="AX230" t="n">
         <v>2</v>
       </c>
-      <c r="AX230" t="inlineStr">
+      <c r="AY230" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -36435,10 +37585,15 @@
       <c r="AV231" t="n">
         <v>1.706493515652707</v>
       </c>
-      <c r="AW231" t="n">
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>10.1039/D3NJ00221G</t>
+        </is>
+      </c>
+      <c r="AX231" t="n">
         <v>2</v>
       </c>
-      <c r="AX231" t="inlineStr">
+      <c r="AY231" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -36581,10 +37736,15 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AU232" t="inlineStr"/>
       <c r="AV232" t="inlineStr"/>
-      <c r="AW232" t="n">
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.8b02132</t>
+        </is>
+      </c>
+      <c r="AX232" t="n">
         <v>2</v>
       </c>
-      <c r="AX232" t="inlineStr">
+      <c r="AY232" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -36727,10 +37887,15 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AU233" t="inlineStr"/>
       <c r="AV233" t="inlineStr"/>
-      <c r="AW233" t="n">
+      <c r="AW233" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.8b02132</t>
+        </is>
+      </c>
+      <c r="AX233" t="n">
         <v>2</v>
       </c>
-      <c r="AX233" t="inlineStr">
+      <c r="AY233" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -36873,10 +38038,15 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AU234" t="inlineStr"/>
       <c r="AV234" t="inlineStr"/>
-      <c r="AW234" t="n">
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t>10.1039/C8RA09241A</t>
+        </is>
+      </c>
+      <c r="AX234" t="n">
         <v>2</v>
       </c>
-      <c r="AX234" t="inlineStr">
+      <c r="AY234" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -37019,10 +38189,15 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AU235" t="inlineStr"/>
       <c r="AV235" t="inlineStr"/>
-      <c r="AW235" t="n">
+      <c r="AW235" t="inlineStr">
+        <is>
+          <t>10.1039/C8RA09241A</t>
+        </is>
+      </c>
+      <c r="AX235" t="n">
         <v>2</v>
       </c>
-      <c r="AX235" t="inlineStr">
+      <c r="AY235" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -37165,10 +38340,15 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AU236" t="inlineStr"/>
       <c r="AV236" t="inlineStr"/>
-      <c r="AW236" t="n">
+      <c r="AW236" t="inlineStr">
+        <is>
+          <t>10.1039/C8RA09241A</t>
+        </is>
+      </c>
+      <c r="AX236" t="n">
         <v>2</v>
       </c>
-      <c r="AX236" t="inlineStr">
+      <c r="AY236" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -37311,10 +38491,15 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AU237" t="inlineStr"/>
       <c r="AV237" t="inlineStr"/>
-      <c r="AW237" t="n">
+      <c r="AW237" t="inlineStr">
+        <is>
+          <t>10.1039/C8RA09241A</t>
+        </is>
+      </c>
+      <c r="AX237" t="n">
         <v>2</v>
       </c>
-      <c r="AX237" t="inlineStr">
+      <c r="AY237" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -37457,10 +38642,15 @@
       <c r="AT238" t="inlineStr"/>
       <c r="AU238" t="inlineStr"/>
       <c r="AV238" t="inlineStr"/>
-      <c r="AW238" t="n">
+      <c r="AW238" t="inlineStr">
+        <is>
+          <t>10.1039/C8RA09241A</t>
+        </is>
+      </c>
+      <c r="AX238" t="n">
         <v>2</v>
       </c>
-      <c r="AX238" t="inlineStr">
+      <c r="AY238" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -37603,10 +38793,15 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AU239" t="inlineStr"/>
       <c r="AV239" t="inlineStr"/>
-      <c r="AW239" t="n">
+      <c r="AW239" t="inlineStr">
+        <is>
+          <t>10.1039/C8RA09241A</t>
+        </is>
+      </c>
+      <c r="AX239" t="n">
         <v>2</v>
       </c>
-      <c r="AX239" t="inlineStr">
+      <c r="AY239" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -37759,10 +38954,15 @@
       <c r="AV240" t="n">
         <v>3.757691144708424</v>
       </c>
-      <c r="AW240" t="n">
+      <c r="AW240" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b01212</t>
+        </is>
+      </c>
+      <c r="AX240" t="n">
         <v>2</v>
       </c>
-      <c r="AX240" t="inlineStr">
+      <c r="AY240" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -37913,10 +39113,15 @@
       <c r="AV241" t="n">
         <v>2.076870410367171</v>
       </c>
-      <c r="AW241" t="n">
+      <c r="AW241" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b01212</t>
+        </is>
+      </c>
+      <c r="AX241" t="n">
         <v>2</v>
       </c>
-      <c r="AX241" t="inlineStr">
+      <c r="AY241" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -38069,10 +39274,15 @@
       <c r="AV242" t="n">
         <v>5.535637149028079</v>
       </c>
-      <c r="AW242" t="n">
+      <c r="AW242" t="inlineStr">
+        <is>
+          <t>10.1002/ceat.201700500</t>
+        </is>
+      </c>
+      <c r="AX242" t="n">
         <v>2</v>
       </c>
-      <c r="AX242" t="inlineStr">
+      <c r="AY242" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -38225,10 +39435,15 @@
       <c r="AV243" t="n">
         <v>1.279067674586033</v>
       </c>
-      <c r="AW243" t="n">
+      <c r="AW243" t="inlineStr">
+        <is>
+          <t>10.1016/j.cattod.2018.06.019</t>
+        </is>
+      </c>
+      <c r="AX243" t="n">
         <v>2</v>
       </c>
-      <c r="AX243" t="inlineStr">
+      <c r="AY243" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -38381,10 +39596,15 @@
       <c r="AV244" t="n">
         <v>1.681659467242621</v>
       </c>
-      <c r="AW244" t="n">
+      <c r="AW244" t="inlineStr">
+        <is>
+          <t>10.1016/j.cattod.2018.06.019</t>
+        </is>
+      </c>
+      <c r="AX244" t="n">
         <v>2</v>
       </c>
-      <c r="AX244" t="inlineStr">
+      <c r="AY244" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -38537,10 +39757,15 @@
       <c r="AV245" t="n">
         <v>0.774</v>
       </c>
-      <c r="AW245" t="n">
+      <c r="AW245" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b03521</t>
+        </is>
+      </c>
+      <c r="AX245" t="n">
         <v>2</v>
       </c>
-      <c r="AX245" t="inlineStr">
+      <c r="AY245" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -38693,10 +39918,15 @@
       <c r="AV246" t="n">
         <v>0.7859999999999999</v>
       </c>
-      <c r="AW246" t="n">
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b03521</t>
+        </is>
+      </c>
+      <c r="AX246" t="n">
         <v>2</v>
       </c>
-      <c r="AX246" t="inlineStr">
+      <c r="AY246" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -38849,10 +40079,15 @@
       <c r="AV247" t="n">
         <v>0.792</v>
       </c>
-      <c r="AW247" t="n">
+      <c r="AW247" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b03521</t>
+        </is>
+      </c>
+      <c r="AX247" t="n">
         <v>2</v>
       </c>
-      <c r="AX247" t="inlineStr">
+      <c r="AY247" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -39005,10 +40240,15 @@
       <c r="AV248" t="n">
         <v>0.846</v>
       </c>
-      <c r="AW248" t="n">
+      <c r="AW248" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b03521</t>
+        </is>
+      </c>
+      <c r="AX248" t="n">
         <v>2</v>
       </c>
-      <c r="AX248" t="inlineStr">
+      <c r="AY248" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -39161,10 +40401,15 @@
       <c r="AV249" t="n">
         <v>0.9059999999999999</v>
       </c>
-      <c r="AW249" t="n">
+      <c r="AW249" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b03521</t>
+        </is>
+      </c>
+      <c r="AX249" t="n">
         <v>2</v>
       </c>
-      <c r="AX249" t="inlineStr">
+      <c r="AY249" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -39317,10 +40562,15 @@
       <c r="AV250" t="n">
         <v>0.918</v>
       </c>
-      <c r="AW250" t="n">
+      <c r="AW250" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b03521</t>
+        </is>
+      </c>
+      <c r="AX250" t="n">
         <v>2</v>
       </c>
-      <c r="AX250" t="inlineStr">
+      <c r="AY250" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -39473,10 +40723,15 @@
       <c r="AV251" t="n">
         <v>0.9419999999999999</v>
       </c>
-      <c r="AW251" t="n">
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b03521</t>
+        </is>
+      </c>
+      <c r="AX251" t="n">
         <v>2</v>
       </c>
-      <c r="AX251" t="inlineStr">
+      <c r="AY251" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -39629,10 +40884,15 @@
       <c r="AV252" t="n">
         <v>1.014</v>
       </c>
-      <c r="AW252" t="n">
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b03521</t>
+        </is>
+      </c>
+      <c r="AX252" t="n">
         <v>2</v>
       </c>
-      <c r="AX252" t="inlineStr">
+      <c r="AY252" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -39785,10 +41045,15 @@
       <c r="AV253" t="n">
         <v>1.044</v>
       </c>
-      <c r="AW253" t="n">
+      <c r="AW253" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b03521</t>
+        </is>
+      </c>
+      <c r="AX253" t="n">
         <v>2</v>
       </c>
-      <c r="AX253" t="inlineStr">
+      <c r="AY253" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -39941,10 +41206,15 @@
       <c r="AV254" t="n">
         <v>1.116</v>
       </c>
-      <c r="AW254" t="n">
+      <c r="AW254" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b03521</t>
+        </is>
+      </c>
+      <c r="AX254" t="n">
         <v>2</v>
       </c>
-      <c r="AX254" t="inlineStr">
+      <c r="AY254" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -40089,10 +41359,15 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AU255" t="inlineStr"/>
       <c r="AV255" t="inlineStr"/>
-      <c r="AW255" t="n">
+      <c r="AW255" t="inlineStr">
+        <is>
+          <t>10.1109/NAP.2017.8190167</t>
+        </is>
+      </c>
+      <c r="AX255" t="n">
         <v>2</v>
       </c>
-      <c r="AX255" t="inlineStr">
+      <c r="AY255" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -40237,10 +41512,15 @@
       <c r="AT256" t="inlineStr"/>
       <c r="AU256" t="inlineStr"/>
       <c r="AV256" t="inlineStr"/>
-      <c r="AW256" t="n">
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>10.1109/NAP.2017.8190167</t>
+        </is>
+      </c>
+      <c r="AX256" t="n">
         <v>2</v>
       </c>
-      <c r="AX256" t="inlineStr">
+      <c r="AY256" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -40385,10 +41665,15 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AU257" t="inlineStr"/>
       <c r="AV257" t="inlineStr"/>
-      <c r="AW257" t="n">
+      <c r="AW257" t="inlineStr">
+        <is>
+          <t>10.1109/NAP.2017.8190167</t>
+        </is>
+      </c>
+      <c r="AX257" t="n">
         <v>2</v>
       </c>
-      <c r="AX257" t="inlineStr">
+      <c r="AY257" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -40531,10 +41816,15 @@
       <c r="AT258" t="inlineStr"/>
       <c r="AU258" t="inlineStr"/>
       <c r="AV258" t="inlineStr"/>
-      <c r="AW258" t="n">
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>10.1007/s11237-020-09658-y</t>
+        </is>
+      </c>
+      <c r="AX258" t="n">
         <v>2</v>
       </c>
-      <c r="AX258" t="inlineStr">
+      <c r="AY258" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -40687,10 +41977,15 @@
       <c r="AV259" t="n">
         <v>0.0452915766738661</v>
       </c>
-      <c r="AW259" t="n">
+      <c r="AW259" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
+      <c r="AX259" t="n">
         <v>2</v>
       </c>
-      <c r="AX259" t="inlineStr">
+      <c r="AY259" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -40843,10 +42138,15 @@
       <c r="AV260" t="n">
         <v>1.092253912062934</v>
       </c>
-      <c r="AW260" t="n">
+      <c r="AW260" t="inlineStr">
+        <is>
+          <t>10.1038/s41598-019-53180-8</t>
+        </is>
+      </c>
+      <c r="AX260" t="n">
         <v>2</v>
       </c>
-      <c r="AX260" t="inlineStr">
+      <c r="AY260" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -40997,10 +42297,15 @@
       <c r="AV261" t="n">
         <v>3.275443272788073</v>
       </c>
-      <c r="AW261" t="n">
+      <c r="AW261" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiec.2016.06.018</t>
+        </is>
+      </c>
+      <c r="AX261" t="n">
         <v>2</v>
       </c>
-      <c r="AX261" t="inlineStr">
+      <c r="AY261" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -41151,10 +42456,15 @@
       <c r="AV262" t="n">
         <v>5.409777999837072</v>
       </c>
-      <c r="AW262" t="n">
+      <c r="AW262" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiec.2016.06.018</t>
+        </is>
+      </c>
+      <c r="AX262" t="n">
         <v>2</v>
       </c>
-      <c r="AX262" t="inlineStr">
+      <c r="AY262" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -41309,10 +42619,15 @@
       <c r="AV263" t="n">
         <v>0.8473623668792444</v>
       </c>
-      <c r="AW263" t="n">
+      <c r="AW263" t="inlineStr">
+        <is>
+          <t>10.1038/s41598-019-53180-8</t>
+        </is>
+      </c>
+      <c r="AX263" t="n">
         <v>2</v>
       </c>
-      <c r="AX263" t="inlineStr">
+      <c r="AY263" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -41465,10 +42780,15 @@
       <c r="AV264" t="n">
         <v>1.497223641843269</v>
       </c>
-      <c r="AW264" t="n">
+      <c r="AW264" t="inlineStr">
+        <is>
+          <t>10.1038/s41598-019-53180-8</t>
+        </is>
+      </c>
+      <c r="AX264" t="n">
         <v>2</v>
       </c>
-      <c r="AX264" t="inlineStr">
+      <c r="AY264" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -41621,10 +42941,15 @@
       <c r="AV265" t="n">
         <v>1.342631167931669</v>
       </c>
-      <c r="AW265" t="n">
+      <c r="AW265" t="inlineStr">
+        <is>
+          <t>10.1038/s41598-019-53180-8</t>
+        </is>
+      </c>
+      <c r="AX265" t="n">
         <v>2</v>
       </c>
-      <c r="AX265" t="inlineStr">
+      <c r="AY265" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -41777,10 +43102,15 @@
       <c r="AV266" t="n">
         <v>3.221065796579677</v>
       </c>
-      <c r="AW266" t="n">
+      <c r="AW266" t="inlineStr">
+        <is>
+          <t>10.1038/s41598-019-53180-8</t>
+        </is>
+      </c>
+      <c r="AX266" t="n">
         <v>2</v>
       </c>
-      <c r="AX266" t="inlineStr">
+      <c r="AY266" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -41931,10 +43261,15 @@
         <v>0.3843130724396337</v>
       </c>
       <c r="AV267" t="inlineStr"/>
-      <c r="AW267" t="n">
+      <c r="AW267" t="inlineStr">
+        <is>
+          <t>10.1038/s41598-019-53180-8</t>
+        </is>
+      </c>
+      <c r="AX267" t="n">
         <v>2</v>
       </c>
-      <c r="AX267" t="inlineStr">
+      <c r="AY267" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -42087,10 +43422,15 @@
       <c r="AV268" t="n">
         <v>0.6770641338786256</v>
       </c>
-      <c r="AW268" t="n">
+      <c r="AW268" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.5b01422</t>
+        </is>
+      </c>
+      <c r="AX268" t="n">
         <v>2</v>
       </c>
-      <c r="AX268" t="inlineStr">
+      <c r="AY268" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -42243,10 +43583,15 @@
       <c r="AV269" t="n">
         <v>0.5234107665098233</v>
       </c>
-      <c r="AW269" t="n">
+      <c r="AW269" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.5b01422</t>
+        </is>
+      </c>
+      <c r="AX269" t="n">
         <v>2</v>
       </c>
-      <c r="AX269" t="inlineStr">
+      <c r="AY269" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -42399,10 +43744,15 @@
       <c r="AV270" t="n">
         <v>0.6770641338786256</v>
       </c>
-      <c r="AW270" t="n">
+      <c r="AW270" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2016.04.107</t>
+        </is>
+      </c>
+      <c r="AX270" t="n">
         <v>2</v>
       </c>
-      <c r="AX270" t="inlineStr">
+      <c r="AY270" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -42555,10 +43905,15 @@
       <c r="AV271" t="n">
         <v>0.9456167857111814</v>
       </c>
-      <c r="AW271" t="n">
+      <c r="AW271" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2016.04.107</t>
+        </is>
+      </c>
+      <c r="AX271" t="n">
         <v>2</v>
       </c>
-      <c r="AX271" t="inlineStr">
+      <c r="AY271" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -42711,10 +44066,15 @@
       <c r="AV272" t="n">
         <v>0.6542116630669548</v>
       </c>
-      <c r="AW272" t="n">
+      <c r="AW272" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
+      <c r="AX272" t="n">
         <v>2</v>
       </c>
-      <c r="AX272" t="inlineStr">
+      <c r="AY272" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -42859,10 +44219,15 @@
       <c r="AT273" t="inlineStr"/>
       <c r="AU273" t="inlineStr"/>
       <c r="AV273" t="inlineStr"/>
-      <c r="AW273" t="n">
+      <c r="AW273" t="inlineStr">
+        <is>
+          <t>10.15587/1729-4061.2015.37405</t>
+        </is>
+      </c>
+      <c r="AX273" t="n">
         <v>2</v>
       </c>
-      <c r="AX273" t="inlineStr">
+      <c r="AY273" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -43007,10 +44372,15 @@
       <c r="AT274" t="inlineStr"/>
       <c r="AU274" t="inlineStr"/>
       <c r="AV274" t="inlineStr"/>
-      <c r="AW274" t="n">
+      <c r="AW274" t="inlineStr">
+        <is>
+          <t>10.1016/j.apcata.2020.117472</t>
+        </is>
+      </c>
+      <c r="AX274" t="n">
         <v>2</v>
       </c>
-      <c r="AX274" t="inlineStr">
+      <c r="AY274" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -43155,10 +44525,15 @@
       <c r="AT275" t="inlineStr"/>
       <c r="AU275" t="inlineStr"/>
       <c r="AV275" t="inlineStr"/>
-      <c r="AW275" t="n">
+      <c r="AW275" t="inlineStr">
+        <is>
+          <t>10.1016/j.apcata.2020.117472</t>
+        </is>
+      </c>
+      <c r="AX275" t="n">
         <v>2</v>
       </c>
-      <c r="AX275" t="inlineStr">
+      <c r="AY275" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -43303,10 +44678,15 @@
       <c r="AT276" t="inlineStr"/>
       <c r="AU276" t="inlineStr"/>
       <c r="AV276" t="inlineStr"/>
-      <c r="AW276" t="n">
+      <c r="AW276" t="inlineStr">
+        <is>
+          <t>10.1007/s11237-020-09658-y</t>
+        </is>
+      </c>
+      <c r="AX276" t="n">
         <v>2</v>
       </c>
-      <c r="AX276" t="inlineStr">
+      <c r="AY276" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -43451,10 +44831,15 @@
       <c r="AT277" t="inlineStr"/>
       <c r="AU277" t="inlineStr"/>
       <c r="AV277" t="inlineStr"/>
-      <c r="AW277" t="n">
+      <c r="AW277" t="inlineStr">
+        <is>
+          <t>10.1007/s11237-020-09658-y</t>
+        </is>
+      </c>
+      <c r="AX277" t="n">
         <v>2</v>
       </c>
-      <c r="AX277" t="inlineStr">
+      <c r="AY277" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -43605,10 +44990,15 @@
       <c r="AV278" t="n">
         <v>2.003826076275772</v>
       </c>
-      <c r="AW278" t="n">
+      <c r="AW278" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiec.2016.06.018</t>
+        </is>
+      </c>
+      <c r="AX278" t="n">
         <v>2</v>
       </c>
-      <c r="AX278" t="inlineStr">
+      <c r="AY278" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -43759,10 +45149,15 @@
       <c r="AV279" t="n">
         <v>2.893351550265347</v>
       </c>
-      <c r="AW279" t="n">
+      <c r="AW279" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiec.2016.06.018</t>
+        </is>
+      </c>
+      <c r="AX279" t="n">
         <v>2</v>
       </c>
-      <c r="AX279" t="inlineStr">
+      <c r="AY279" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -43915,10 +45310,15 @@
       <c r="AV280" t="n">
         <v>7.685634535477528</v>
       </c>
-      <c r="AW280" t="n">
+      <c r="AW280" t="inlineStr">
+        <is>
+          <t>10.1039/C7RA09778F</t>
+        </is>
+      </c>
+      <c r="AX280" t="n">
         <v>2</v>
       </c>
-      <c r="AX280" t="inlineStr">
+      <c r="AY280" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -44071,10 +45471,15 @@
       <c r="AV281" t="n">
         <v>10.10657531639547</v>
       </c>
-      <c r="AW281" t="n">
+      <c r="AW281" t="inlineStr">
+        <is>
+          <t>10.1039/C7RA09778F</t>
+        </is>
+      </c>
+      <c r="AX281" t="n">
         <v>2</v>
       </c>
-      <c r="AX281" t="inlineStr">
+      <c r="AY281" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -44227,10 +45632,15 @@
       <c r="AV282" t="n">
         <v>10.46241951343293</v>
       </c>
-      <c r="AW282" t="n">
+      <c r="AW282" t="inlineStr">
+        <is>
+          <t>10.1039/C7RA09778F</t>
+        </is>
+      </c>
+      <c r="AX282" t="n">
         <v>2</v>
       </c>
-      <c r="AX282" t="inlineStr">
+      <c r="AY282" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -44383,10 +45793,15 @@
       <c r="AV283" t="n">
         <v>9.635344308053416</v>
       </c>
-      <c r="AW283" t="n">
+      <c r="AW283" t="inlineStr">
+        <is>
+          <t>10.1039/C7RA09778F</t>
+        </is>
+      </c>
+      <c r="AX283" t="n">
         <v>2</v>
       </c>
-      <c r="AX283" t="inlineStr">
+      <c r="AY283" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -44529,10 +45944,15 @@
       <c r="AT284" t="inlineStr"/>
       <c r="AU284" t="inlineStr"/>
       <c r="AV284" t="inlineStr"/>
-      <c r="AW284" t="n">
+      <c r="AW284" t="inlineStr">
+        <is>
+          <t>10.4028/www.scientific.net/AMR.233-235.2859</t>
+        </is>
+      </c>
+      <c r="AX284" t="n">
         <v>2</v>
       </c>
-      <c r="AX284" t="inlineStr">
+      <c r="AY284" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -44675,10 +46095,15 @@
       <c r="AT285" t="inlineStr"/>
       <c r="AU285" t="inlineStr"/>
       <c r="AV285" t="inlineStr"/>
-      <c r="AW285" t="n">
+      <c r="AW285" t="inlineStr">
+        <is>
+          <t>10.4028/www.scientific.net/AMR.233-235.2859</t>
+        </is>
+      </c>
+      <c r="AX285" t="n">
         <v>2</v>
       </c>
-      <c r="AX285" t="inlineStr">
+      <c r="AY285" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -44831,10 +46256,15 @@
       <c r="AV286" t="n">
         <v>13.68434038301416</v>
       </c>
-      <c r="AW286" t="n">
+      <c r="AW286" t="inlineStr">
+        <is>
+          <t>10.1016/j.apcata.2023.119441</t>
+        </is>
+      </c>
+      <c r="AX286" t="n">
         <v>2</v>
       </c>
-      <c r="AX286" t="inlineStr">
+      <c r="AY286" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -44987,10 +46417,15 @@
       <c r="AV287" t="n">
         <v>17.33580195004163</v>
       </c>
-      <c r="AW287" t="n">
+      <c r="AW287" t="inlineStr">
+        <is>
+          <t>10.1016/j.apcata.2023.119441</t>
+        </is>
+      </c>
+      <c r="AX287" t="n">
         <v>2</v>
       </c>
-      <c r="AX287" t="inlineStr">
+      <c r="AY287" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -45143,10 +46578,15 @@
       <c r="AV288" t="n">
         <v>17.54505867110741</v>
       </c>
-      <c r="AW288" t="n">
+      <c r="AW288" t="inlineStr">
+        <is>
+          <t>10.1016/j.apcata.2023.119441</t>
+        </is>
+      </c>
+      <c r="AX288" t="n">
         <v>2</v>
       </c>
-      <c r="AX288" t="inlineStr">
+      <c r="AY288" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -45299,10 +46739,15 @@
       <c r="AV289" t="n">
         <v>18.07017357202331</v>
       </c>
-      <c r="AW289" t="n">
+      <c r="AW289" t="inlineStr">
+        <is>
+          <t>10.1016/j.apcata.2023.119441</t>
+        </is>
+      </c>
+      <c r="AX289" t="n">
         <v>2</v>
       </c>
-      <c r="AX289" t="inlineStr">
+      <c r="AY289" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -45455,10 +46900,15 @@
       <c r="AV290" t="n">
         <v>19.06192839300583</v>
       </c>
-      <c r="AW290" t="n">
+      <c r="AW290" t="inlineStr">
+        <is>
+          <t>10.1016/j.apcata.2023.119441</t>
+        </is>
+      </c>
+      <c r="AX290" t="n">
         <v>2</v>
       </c>
-      <c r="AX290" t="inlineStr">
+      <c r="AY290" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -45611,10 +47061,15 @@
       <c r="AV291" t="n">
         <v>2.420641408831346</v>
       </c>
-      <c r="AW291" t="n">
+      <c r="AW291" t="inlineStr">
+        <is>
+          <t>10.1039/C9CC08700A</t>
+        </is>
+      </c>
+      <c r="AX291" t="n">
         <v>2</v>
       </c>
-      <c r="AX291" t="inlineStr">
+      <c r="AY291" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -45767,10 +47222,15 @@
       <c r="AV292" t="n">
         <v>2.880256866204387</v>
       </c>
-      <c r="AW292" t="n">
+      <c r="AW292" t="inlineStr">
+        <is>
+          <t>10.1039/C9CC08700A</t>
+        </is>
+      </c>
+      <c r="AX292" t="n">
         <v>2</v>
       </c>
-      <c r="AX292" t="inlineStr">
+      <c r="AY292" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -45923,10 +47383,15 @@
       <c r="AV293" t="n">
         <v>3.125385110136675</v>
       </c>
-      <c r="AW293" t="n">
+      <c r="AW293" t="inlineStr">
+        <is>
+          <t>10.1039/C9CC08700A</t>
+        </is>
+      </c>
+      <c r="AX293" t="n">
         <v>2</v>
       </c>
-      <c r="AX293" t="inlineStr">
+      <c r="AY293" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -46079,10 +47544,15 @@
       <c r="AV294" t="n">
         <v>3.033462018662067</v>
       </c>
-      <c r="AW294" t="n">
+      <c r="AW294" t="inlineStr">
+        <is>
+          <t>10.1039/C9CC08700A</t>
+        </is>
+      </c>
+      <c r="AX294" t="n">
         <v>2</v>
       </c>
-      <c r="AX294" t="inlineStr">
+      <c r="AY294" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -46227,10 +47697,15 @@
       <c r="AT295" t="inlineStr"/>
       <c r="AU295" t="inlineStr"/>
       <c r="AV295" t="inlineStr"/>
-      <c r="AW295" t="n">
+      <c r="AW295" t="inlineStr">
+        <is>
+          <t>10.1007/s11237-020-09658-y</t>
+        </is>
+      </c>
+      <c r="AX295" t="n">
         <v>2</v>
       </c>
-      <c r="AX295" t="inlineStr">
+      <c r="AY295" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -46383,10 +47858,15 @@
       <c r="AV296" t="n">
         <v>1.01056186830644</v>
       </c>
-      <c r="AW296" t="n">
+      <c r="AW296" t="inlineStr">
+        <is>
+          <t>10.1021/acssuschemeng.0c05916</t>
+        </is>
+      </c>
+      <c r="AX296" t="n">
         <v>2</v>
       </c>
-      <c r="AX296" t="inlineStr">
+      <c r="AY296" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -46539,10 +48019,15 @@
       <c r="AV297" t="n">
         <v>1.450154752798345</v>
       </c>
-      <c r="AW297" t="n">
+      <c r="AW297" t="inlineStr">
+        <is>
+          <t>10.1021/acssuschemeng.0c05916</t>
+        </is>
+      </c>
+      <c r="AX297" t="n">
         <v>2</v>
       </c>
-      <c r="AX297" t="inlineStr">
+      <c r="AY297" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -46695,10 +48180,15 @@
       <c r="AV298" t="n">
         <v>0.6014824710166493</v>
       </c>
-      <c r="AW298" t="n">
+      <c r="AW298" t="inlineStr">
+        <is>
+          <t>10.1021/acssuschemeng.0c05916</t>
+        </is>
+      </c>
+      <c r="AX298" t="n">
         <v>2</v>
       </c>
-      <c r="AX298" t="inlineStr">
+      <c r="AY298" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -46851,10 +48341,15 @@
       <c r="AV299" t="n">
         <v>0.6327753511306047</v>
       </c>
-      <c r="AW299" t="n">
+      <c r="AW299" t="inlineStr">
+        <is>
+          <t>10.1021/acssuschemeng.0c05916</t>
+        </is>
+      </c>
+      <c r="AX299" t="n">
         <v>2</v>
       </c>
-      <c r="AX299" t="inlineStr">
+      <c r="AY299" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -47007,10 +48502,15 @@
       <c r="AV300" t="n">
         <v>0.4906587473002161</v>
       </c>
-      <c r="AW300" t="n">
+      <c r="AW300" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
+      <c r="AX300" t="n">
         <v>2</v>
       </c>
-      <c r="AX300" t="inlineStr">
+      <c r="AY300" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -47155,10 +48655,15 @@
       <c r="AT301" t="inlineStr"/>
       <c r="AU301" t="inlineStr"/>
       <c r="AV301" t="inlineStr"/>
-      <c r="AW301" t="n">
+      <c r="AW301" t="inlineStr">
+        <is>
+          <t>10.1007/s11237-020-09658-y</t>
+        </is>
+      </c>
+      <c r="AX301" t="n">
         <v>2</v>
       </c>
-      <c r="AX301" t="inlineStr">
+      <c r="AY301" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -47313,10 +48818,15 @@
       <c r="AV302" t="n">
         <v>7.869421565362199</v>
       </c>
-      <c r="AW302" t="n">
+      <c r="AW302" t="inlineStr">
+        <is>
+          <t>10.19906/j.cnki.JFCT.2022036</t>
+        </is>
+      </c>
+      <c r="AX302" t="n">
         <v>2</v>
       </c>
-      <c r="AX302" t="inlineStr">
+      <c r="AY302" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -47469,10 +48979,15 @@
       <c r="AV303" t="n">
         <v>0.4977041036717064</v>
       </c>
-      <c r="AW303" t="n">
+      <c r="AW303" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
+      <c r="AX303" t="n">
         <v>2</v>
       </c>
-      <c r="AX303" t="inlineStr">
+      <c r="AY303" t="inlineStr">
         <is>
           <t>P-V-Ti</t>
         </is>
@@ -47625,10 +49140,15 @@
       <c r="AV304" t="n">
         <v>4.775040441526312</v>
       </c>
-      <c r="AW304" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX304" t="inlineStr">
+      <c r="AW304" t="inlineStr">
+        <is>
+          <t>10.1002/jctb.6360</t>
+        </is>
+      </c>
+      <c r="AX304" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY304" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -47773,10 +49293,15 @@
       <c r="AT305" t="inlineStr"/>
       <c r="AU305" t="inlineStr"/>
       <c r="AV305" t="inlineStr"/>
-      <c r="AW305" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX305" t="inlineStr">
+      <c r="AW305" t="inlineStr">
+        <is>
+          <t>10.15587/1729-4061.2013.19130</t>
+        </is>
+      </c>
+      <c r="AX305" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY305" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -47929,10 +49454,15 @@
       <c r="AV306" t="n">
         <v>5.648172043010754</v>
       </c>
-      <c r="AW306" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX306" t="inlineStr">
+      <c r="AW306" t="inlineStr">
+        <is>
+          <t>10.1002/jctb.6360</t>
+        </is>
+      </c>
+      <c r="AX306" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY306" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -48085,10 +49615,15 @@
       <c r="AV307" t="n">
         <v>0.2511166306695465</v>
       </c>
-      <c r="AW307" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX307" t="inlineStr">
+      <c r="AW307" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6b03079</t>
+        </is>
+      </c>
+      <c r="AX307" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY307" t="inlineStr">
         <is>
           <t>Al-Cs-Ti</t>
         </is>
@@ -48241,10 +49776,15 @@
       <c r="AV308" t="n">
         <v>1.212167332354212</v>
       </c>
-      <c r="AW308" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX308" t="inlineStr">
+      <c r="AW308" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
+      <c r="AX308" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY308" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -48397,10 +49937,15 @@
       <c r="AV309" t="n">
         <v>0.9152924607343416</v>
       </c>
-      <c r="AW309" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX309" t="inlineStr">
+      <c r="AW309" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
+      <c r="AX309" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY309" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -48553,10 +50098,15 @@
       <c r="AV310" t="n">
         <v>1.209156348336933</v>
       </c>
-      <c r="AW310" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX310" t="inlineStr">
+      <c r="AW310" t="inlineStr">
+        <is>
+          <t>10.1002/cjce.22889</t>
+        </is>
+      </c>
+      <c r="AX310" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY310" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -48707,10 +50257,15 @@
       <c r="AV311" t="n">
         <v>0.7289173602215658</v>
       </c>
-      <c r="AW311" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX311" t="inlineStr">
+      <c r="AW311" t="inlineStr">
+        <is>
+          <t>10.1016/j.micromeso.2017.07.045</t>
+        </is>
+      </c>
+      <c r="AX311" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY311" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -48861,10 +50416,15 @@
       <c r="AV312" t="n">
         <v>0.7658212206013317</v>
       </c>
-      <c r="AW312" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX312" t="inlineStr">
+      <c r="AW312" t="inlineStr">
+        <is>
+          <t>10.1016/j.micromeso.2017.07.045</t>
+        </is>
+      </c>
+      <c r="AX312" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY312" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -49015,10 +50575,15 @@
       <c r="AV313" t="n">
         <v>0.9793687450907784</v>
       </c>
-      <c r="AW313" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX313" t="inlineStr">
+      <c r="AW313" t="inlineStr">
+        <is>
+          <t>10.1016/j.micromeso.2017.07.045</t>
+        </is>
+      </c>
+      <c r="AX313" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY313" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -49171,10 +50736,15 @@
       <c r="AV314" t="n">
         <v>1.298358531317495</v>
       </c>
-      <c r="AW314" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX314" t="inlineStr">
+      <c r="AW314" t="inlineStr">
+        <is>
+          <t>10.1016/j.micromeso.2017.07.045</t>
+        </is>
+      </c>
+      <c r="AX314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY314" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
@@ -49327,10 +50897,15 @@
       <c r="AV315" t="n">
         <v>1.093485388871236</v>
       </c>
-      <c r="AW315" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX315" t="inlineStr">
+      <c r="AW315" t="inlineStr">
+        <is>
+          <t>10.1016/j.micromeso.2017.07.045</t>
+        </is>
+      </c>
+      <c r="AX315" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY315" t="inlineStr">
         <is>
           <t>Si-Al-Cs</t>
         </is>
